--- a/maintenance/product-assets.xlsx
+++ b/maintenance/product-assets.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商品信息 Products" sheetId="1" r:id="R565aeee771624e2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参考图 References" sheetId="2" r:id="R157b665e66c54cca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图片命名规则" sheetId="3" r:id="Rc546c45e06e24e86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="网站图片需求核对" sheetId="4" r:id="R71ba8689cf85484d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="灵感板 Inspiration" sheetId="5" r:id="Rac2bf3d2072d4f35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图片包清单" sheetId="6" r:id="R4bbe321c96114396"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当前网站现状" sheetId="7" r:id="R94c283f743fb4163"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product29-30" sheetId="8" r:id="Ra3b475085f05459c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商品信息 Products" sheetId="1" r:id="R6065d51bdf154fd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参考图 References" sheetId="2" r:id="R2dffbb84c712452f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图片命名规则" sheetId="3" r:id="Rc383f88cb5a744f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="网站图片需求核对" sheetId="4" r:id="R6a7e902fb787472a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="灵感板 Inspiration" sheetId="5" r:id="R505ee9671b7f4bac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图片包清单" sheetId="6" r:id="Re5efb04db7ef4c57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当前网站现状" sheetId="7" r:id="Rb8f4c9c16daf4c3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product29-30" sheetId="8" r:id="R5932d0b116b64d72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product31-45" sheetId="9" r:id="R3c8b147f0cb74d0f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2043,7 +2044,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="8">
+  <x:fonts count="9">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -2084,8 +2085,14 @@
       <x:color theme="1"/>
       <x:name val="宋体"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="宋体"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -2100,6 +2107,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="111111"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="F3F0E8"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -2131,7 +2143,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="35">
+  <x:cellXfs count="51">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
@@ -2223,6 +2235,44 @@
     <x:xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="2">
     <x:cellStyle name="常规" xfId="0"/>
@@ -2424,58 +2474,58 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="11" t="s">
+      <x:c r="A1" s="47" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B1" s="11" t="s">
+      <x:c r="B1" s="47" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C1" s="11" t="s">
+      <x:c r="C1" s="47" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D1" s="11" t="s">
+      <x:c r="D1" s="47" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E1" s="11" t="s">
+      <x:c r="E1" s="47" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F1" s="11" t="s">
+      <x:c r="F1" s="47" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G1" s="11" t="s">
+      <x:c r="G1" s="47" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H1" s="11" t="s">
+      <x:c r="H1" s="47" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I1" s="11" t="s">
+      <x:c r="I1" s="47" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J1" s="11" t="s">
+      <x:c r="J1" s="47" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K1" s="11" t="s">
+      <x:c r="K1" s="47" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L1" s="11" t="s">
+      <x:c r="L1" s="47" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M1" s="11" t="s">
+      <x:c r="M1" s="47" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="N1" s="11" t="s">
+      <x:c r="N1" s="47" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="O1" s="11" t="s">
+      <x:c r="O1" s="47" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="P1" s="11" t="s">
+      <x:c r="P1" s="47" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="Q1" s="11" t="s">
+      <x:c r="Q1" s="47" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="R1" s="11" t="s">
+      <x:c r="R1" s="47" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>
@@ -3955,49 +4005,774 @@
       </x:c>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="1"/>
+      <x:c r="A32" s="1" t="str">
+        <x:v>P031</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>景观人物/植物素材</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>product31</x:v>
+      </x:c>
+      <x:c r="D32" t="str">
+        <x:v>Plant Assets</x:v>
+      </x:c>
+      <x:c r="E32" t="str">
+        <x:v>01-cover.webp</x:v>
+      </x:c>
+      <x:c r="F32" t="str">
+        <x:v>02-detail-01.webp</x:v>
+      </x:c>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+      <x:c r="I32"/>
+      <x:c r="J32"/>
+      <x:c r="K32" t="n">
+        <x:v>9.9</x:v>
+      </x:c>
+      <x:c r="L32" t="str">
+        <x:v>https://item.taobao.com/item.htm?id=930207470556&amp;pisk=glu-WRfgJIC8KGLXBaxmxGe4gYu-yncrkYl1-J2lAxHxOYwuK7Z7GiNuwawCVXNQJxMHa8cBUv3LhvRP-QuopkGunvbnZ2nVJflErQzHazcz8y9MIFYiabzFjm_Tr4Qfh7cfVasWmrwGOS5yIFYiabzURdvixBUB17NGRys7FtOY95bQRg_WM-NL_J_SdyOvM5VFAgaQR-sb9-15PyZIGtNa_Js7NWOxG-PQRJMQVIhb3WaQdB1BDJS7IwnVUleiLFFVRwgYwoZmNS1b8qN86REfxw_CT7E8CbwXECShJkH82qYRQ7nj65F-DBsbFj0-97nvOiwSOfuZjgyTIRRNZOm35gdxRMSUVSoR7UMXbIAQ_SeMi7jFYoK4MRAvMMSUVSPYIIVlYMrv0&amp;spm=a1z10.5-c.w4002-25832238778.10.268f4bc7CVKTZ2</x:v>
+      </x:c>
+      <x:c r="M32" t="str">
+        <x:v>People, Plant, Landscape, PNG/AI</x:v>
+      </x:c>
+      <x:c r="N32" t="str">
+        <x:v>植物人物素材</x:v>
+      </x:c>
+      <x:c r="O32" t="str">
+        <x:v>景观人物与植物素材合集，适合平面、分析图和场景氛围表达。</x:v>
+      </x:c>
+      <x:c r="P32" t="str">
+        <x:v>PNG / AI</x:v>
+      </x:c>
+      <x:c r="Q32" t="str">
+        <x:v>景观/建筑/环艺设计、作品集、人物与植物素材</x:v>
+      </x:c>
+      <x:c r="R32" t="str">
+        <x:v>新增 product31；图片已转 WebP 并接入网站。</x:v>
+      </x:c>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="1"/>
+      <x:c r="A33" s="1" t="str">
+        <x:v>P032</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>黑白人物素材</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>product32</x:v>
+      </x:c>
+      <x:c r="D33" t="str">
+        <x:v>People Assets</x:v>
+      </x:c>
+      <x:c r="E33" t="str">
+        <x:v>01-cover.webp</x:v>
+      </x:c>
+      <x:c r="F33"/>
+      <x:c r="G33"/>
+      <x:c r="H33"/>
+      <x:c r="I33"/>
+      <x:c r="J33"/>
+      <x:c r="K33" t="n">
+        <x:v>8.8</x:v>
+      </x:c>
+      <x:c r="L33" t="str">
+        <x:v>https://item.taobao.com/item.htm?id=930677587099&amp;pisk=hezxeow_r0pN5VClv6FjHX3sJ_X3GPcs15Pw1xgjnCeT_XhX5ftfPYGZMcTG0qmtW8MuoxVmlA3TTJemncx02CFUejBh-x9bzu0ecFGXIbOSih8lhn73gSuZ59Xh-lx-fxlkfFw6cYOSUfx65RtXF_hssKMshRN5wfkSGIg6l0TSOXxs1RtjF7GKTKtX5EN5PjDSCVisG_FSUf3sCRg1w7_0Mm1DqVMG-GD9KnPjeedzyVvnpPM5dorIM9kIjfZPLyFQGylT76ttBxZbAqaOpdm8FoZIlPBpFArmTHP7S_K1buyYY8dCxzUx_WE3dH78W9P3lriyuwUNLWe7NRbJ-zQ3u8uYLp6FJwHbPzUcrEzNtWVaolYFj9s39zyKjh9dH9sjaoLFl8sFZ1GEwvfoih-Z2gl-K_CJbhojabHhZjxwb0IP.&amp;spm=a1z10.5-c.w4002-25832238778.10.906a4bc7Yrsb6B</x:v>
+      </x:c>
+      <x:c r="M33" t="str">
+        <x:v>People, Black White, Figure, PNG/AI</x:v>
+      </x:c>
+      <x:c r="N33" t="str">
+        <x:v>黑白人物素材</x:v>
+      </x:c>
+      <x:c r="O33" t="str">
+        <x:v>黑白人物剪影与线稿素材，适合分析图、平面图和作品集排版。</x:v>
+      </x:c>
+      <x:c r="P33" t="str">
+        <x:v>PNG / AI</x:v>
+      </x:c>
+      <x:c r="Q33" t="str">
+        <x:v>景观/建筑/环艺设计、作品集、人物素材</x:v>
+      </x:c>
+      <x:c r="R33" t="str">
+        <x:v>新增 product32；图片已转 WebP 并接入网站。</x:v>
+      </x:c>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="1"/>
+      <x:c r="A34" s="1" t="str">
+        <x:v>P033</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>高级感分析图模版素材</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>product33</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>Module Diagrams</x:v>
+      </x:c>
+      <x:c r="E34" t="str">
+        <x:v>01-cover.webp</x:v>
+      </x:c>
+      <x:c r="F34" t="str">
+        <x:v>02-detail-01.webp</x:v>
+      </x:c>
+      <x:c r="G34" t="str">
+        <x:v>03-detail-02.webp</x:v>
+      </x:c>
+      <x:c r="H34" t="str">
+        <x:v>04-detail-03.webp</x:v>
+      </x:c>
+      <x:c r="I34" t="str">
+        <x:v>05-detail-04.webp</x:v>
+      </x:c>
+      <x:c r="J34"/>
+      <x:c r="K34" t="n">
+        <x:v>12.8</x:v>
+      </x:c>
+      <x:c r="L34" t="str">
+        <x:v>https://item.taobao.com/item.htm?id=930766101540&amp;pisk=hnsZUBAKwXxL1ytOl7JcbBFQdhB9O1mjcnO_-6RhHsO6cdxHKLJZIcxmSwJcG6eYBh6Dgs5B9Gw9GRhVgtWwosOfCh69Dud24Qj2x9vyEoiiSKAWIpbaN7Z7VOB9DnXfoEaht2vJtAvmSsYn-LdnIffDsecHHKKDisx0LHvXQf0DSdvhKKdnIcxmj20HhKviSIx0L9Ap3Imcin2exBpDmIfDmahj0wh9bFGTSWo2d-9w7ISXTTWuhdVHaOSwpaIE2FSCa-9MnnbGC68577oN-OfNrUjg24LGI17krGqZwBTJYnl-mm1SCWjUtZ7Fyi4S-M4Ph_7AhqFlVP1CEg8oeWsQ9Z6ejwiQKRVHHOBVc0U8ESWd7w6x65VbDBICXT4SpPN50NCl9pJUeKOEWOW9zeuxkFe9LQwMSq3vSppeNJyEkqLTBpR7IFf..&amp;spm=a1z10.5-c.w4002-25832238778.14.2baf4bc7S3d3I9</x:v>
+      </x:c>
+      <x:c r="M34" t="str">
+        <x:v>Module, Diagram, Analysis, AI/Psd</x:v>
+      </x:c>
+      <x:c r="N34" t="str">
+        <x:v>景观分析图</x:v>
+      </x:c>
+      <x:c r="O34" t="str">
+        <x:v>高级感分析图模版素材，适合作品集前期分析、策略图和概念表达。</x:v>
+      </x:c>
+      <x:c r="P34" t="str">
+        <x:v>PNG / PDF / AI</x:v>
+      </x:c>
+      <x:c r="Q34" t="str">
+        <x:v>景观/建筑/环艺设计、作品集、分析图</x:v>
+      </x:c>
+      <x:c r="R34" t="str">
+        <x:v>新增 product33；图片已转 WebP 并接入网站。</x:v>
+      </x:c>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="1"/>
+      <x:c r="A35" s="1" t="str">
+        <x:v>P034</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>插画风动植物/人物素材</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>product34</x:v>
+      </x:c>
+      <x:c r="D35" t="str">
+        <x:v>Animal Assets</x:v>
+      </x:c>
+      <x:c r="E35" t="str">
+        <x:v>01-cover.webp</x:v>
+      </x:c>
+      <x:c r="F35" t="str">
+        <x:v>02-detail-01.webp</x:v>
+      </x:c>
+      <x:c r="G35"/>
+      <x:c r="H35"/>
+      <x:c r="I35"/>
+      <x:c r="J35"/>
+      <x:c r="K35" t="n">
+        <x:v>9.9</x:v>
+      </x:c>
+      <x:c r="L35" t="str">
+        <x:v>https://item.taobao.com/item.htm?id=929792199942&amp;pisk=hIKneTDgKUvMjA3TnrV1R7KHtVnvj8vX3_ELzMRGaBO1wy7FaPoNpT1zLL5RqQAkZ6QrOMKksQRu2eKdvaoPsBrRJwmvdwlydzdhLTSZUtBuTl1tYcpCVglxMmnvd4fDLf0PU_kibTWc4TWPaAmNn1rFUkSP_AX5__SP89yaQ9B489WPTAmNE9VULa7EbcWd3TSP4Q5aQ16P49RP4AvN1T70HpDWM_Y0RqIiczEz4HS5-Fof_vkhtoB1goCi9xa8qaAh-hn3G9YwntXHSYzNTdKHE9YiUP5eUKtXkHouzzPXCppzlVlKnLLhkCzxuhDMHBTWrkyk-XphACtUFvhqt1deFEyx1fhBhBO9_kGwSXAwhLY0n0oZb6LCxZrq4j-JyHMGMyXEDtTwwqftIA42lwW1LmHiIza58O6GMADguE_FC9oA.&amp;spm=a1z10.5-c.w4002-25832238778.16.63a94bc72nZkev</x:v>
+      </x:c>
+      <x:c r="M35" t="str">
+        <x:v>People, Plant, Animal, Illustration</x:v>
+      </x:c>
+      <x:c r="N35" t="str">
+        <x:v>动植物人物素材</x:v>
+      </x:c>
+      <x:c r="O35" t="str">
+        <x:v>插画风动植物与人物素材，适合自然场景、活动氛围和作品集点缀。</x:v>
+      </x:c>
+      <x:c r="P35" t="str">
+        <x:v>PNG / AI</x:v>
+      </x:c>
+      <x:c r="Q35" t="str">
+        <x:v>景观/建筑/环艺设计、作品集、动植物人物素材</x:v>
+      </x:c>
+      <x:c r="R35" t="str">
+        <x:v>新增 product34；图片已转 WebP 并接入网站。</x:v>
+      </x:c>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="1"/>
+      <x:c r="A36" s="1" t="str">
+        <x:v>P035</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>蓝色系人物/植物素材</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>product35</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>People Assets</x:v>
+      </x:c>
+      <x:c r="E36" t="str">
+        <x:v>01-cover.webp</x:v>
+      </x:c>
+      <x:c r="F36" t="str">
+        <x:v>02-detail-01.webp</x:v>
+      </x:c>
+      <x:c r="G36"/>
+      <x:c r="H36"/>
+      <x:c r="I36"/>
+      <x:c r="J36"/>
+      <x:c r="K36" t="n">
+        <x:v>8.8</x:v>
+      </x:c>
+      <x:c r="L36" t="str">
+        <x:v>https://item.taobao.com/item.htm?id=929802023044&amp;pisk=hkziFr1HsdQ0-6IpZ3bIDC4gIMQ8-IV7axL90Vyn3RwIHhoZ3H7E6jM2_Skxo-20nAnVCVU0K-yDklUtWm7qKR8xXcb81dVe6Z2MuAoFgbGj_eMd7wFslqWReaQ81iDusOjZgx5h8jlZujlq36bEav8ZgFuqL6cjLxuq0xueTbGvuKu43woE6fkqgqoqLWlSaqk43jPFtjME_qu43W5nGZv7ssw-dk8Vvq7WDE847qigWaMFCOHMyYDyyvXONnLmmRmgJNvSskPoZfqhgHka9PVmskf2YAP4NzZJYhK20LNQ6S-5YOCuMlm8L3Iz-6V8CoZD7IqGQ7381r9Gitz79oPzNe5CPtZzxSrWqKbRqlZUWWTPCiUgD8qQriKN3truj6DJjf7-NkyAqvCht3rSbXGNy6fHcniZOXDRt6xzVclI_aC..&amp;spm=a1z10.5-c.w4002-25832238778.18.70fb4bc75EebYC</x:v>
+      </x:c>
+      <x:c r="M36" t="str">
+        <x:v>People, Plant, Blue, Illustration</x:v>
+      </x:c>
+      <x:c r="N36" t="str">
+        <x:v>蓝色系人物植物素材</x:v>
+      </x:c>
+      <x:c r="O36" t="str">
+        <x:v>蓝色系人物与植物素材，可用于平面、剖面和分析图的清爽表达。</x:v>
+      </x:c>
+      <x:c r="P36" t="str">
+        <x:v>PNG / AI</x:v>
+      </x:c>
+      <x:c r="Q36" t="str">
+        <x:v>景观/建筑/环艺设计、作品集、人物与植物素材</x:v>
+      </x:c>
+      <x:c r="R36" t="str">
+        <x:v>新增 product35；图片已转 WebP 并接入网站。</x:v>
+      </x:c>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="1"/>
+      <x:c r="A37" s="1" t="str">
+        <x:v>P036</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>高级感前期分析模版</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>product36</x:v>
+      </x:c>
+      <x:c r="D37" t="str">
+        <x:v>Module Diagrams</x:v>
+      </x:c>
+      <x:c r="E37" t="str">
+        <x:v>01-cover.webp</x:v>
+      </x:c>
+      <x:c r="F37" t="str">
+        <x:v>02-detail-01.webp</x:v>
+      </x:c>
+      <x:c r="G37" t="str">
+        <x:v>03-detail-02.webp</x:v>
+      </x:c>
+      <x:c r="H37" t="str">
+        <x:v>04-detail-03.webp</x:v>
+      </x:c>
+      <x:c r="I37" t="str">
+        <x:v>05-detail-04.webp</x:v>
+      </x:c>
+      <x:c r="J37"/>
+      <x:c r="K37" t="n">
+        <x:v>12.8</x:v>
+      </x:c>
+      <x:c r="L37" t="str">
+        <x:v>https://item.taobao.com/item.htm?id=930691571350&amp;pisk=hKeKEu47Ix8AFYIGMiHF4ukS3Gb0A8mSVuryV2MI-3U84mnBF0OCCVirvb9lTvc-ePggK2qnd4H80rUn-bA363E4WDQcnd3emrH2OBgWrc6sDQJGRBW0YkkrFZbcn7AONIowNLaWOf6s70AWFzOB5GnSqegSRzZ1X0usALiWFAis4m9BNzOI5lixvDOBdXg6C0usPYGSRfst4ViIFYa7fGnPrBGCxC4uCd_OYXOF3VpWHoodQqXq5SN0C5LDCk3Tjl0qltA_Vz_JExN4W8hjfTK-XSE_z2ZCe3nTMlatiRYMYD2lXQ1z_yF4Wn10BJnzDS4XgOeRuo2QdfJF3texRRZu5nvgdsgTjWEcZLBcgkkZBJ-lUwfYyuP_GeXNuae75l2eg6sYI6ia9KWQ5sSGVmotoGmHaQlO_c3cXGdyaXiZXqjixQRr615..&amp;spm=a1z10.5-c.w4002-25832238778.28.3d484bc7BCwzHc</x:v>
+      </x:c>
+      <x:c r="M37" t="str">
+        <x:v>Module, Diagram, Analysis, AI/Psd</x:v>
+      </x:c>
+      <x:c r="N37" t="str">
+        <x:v>景观分析图</x:v>
+      </x:c>
+      <x:c r="O37" t="str">
+        <x:v>高级感前期分析模版，适合场地分析、空间关系和设计策略表达。</x:v>
+      </x:c>
+      <x:c r="P37" t="str">
+        <x:v>PNG / PDF / AI</x:v>
+      </x:c>
+      <x:c r="Q37" t="str">
+        <x:v>景观/建筑/环艺设计、作品集、分析图</x:v>
+      </x:c>
+      <x:c r="R37" t="str">
+        <x:v>新增 product36；图片已转 WebP 并接入网站。</x:v>
+      </x:c>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="1"/>
+      <x:c r="A38" s="1" t="str">
+        <x:v>P037</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>拼贴感前期分析模版</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>product37</x:v>
+      </x:c>
+      <x:c r="D38" t="str">
+        <x:v>Module Diagrams</x:v>
+      </x:c>
+      <x:c r="E38" t="str">
+        <x:v>01-cover.webp</x:v>
+      </x:c>
+      <x:c r="F38" t="str">
+        <x:v>02-detail-01.webp</x:v>
+      </x:c>
+      <x:c r="G38" t="str">
+        <x:v>03-detail-02.webp</x:v>
+      </x:c>
+      <x:c r="H38" t="str">
+        <x:v>04-detail-03.webp</x:v>
+      </x:c>
+      <x:c r="I38" t="str">
+        <x:v>05-detail-04.webp</x:v>
+      </x:c>
+      <x:c r="J38"/>
+      <x:c r="K38" t="n">
+        <x:v>12.8</x:v>
+      </x:c>
+      <x:c r="L38" t="str">
+        <x:v>https://item.taobao.com/item.htm?id=931636713263&amp;pisk=hWitUIGjxPrWcopHyLKwDmrb2pAoCm2bhxkVh5Z_sthx38e1c-_6AWw4BrsD7l4YDXNnj5DgfSExUbhgsrbiJtHr9RdkqN-09sZ_CSw_GKsQn-sFxh_ZQAr4cQAkq3YAJvQe1ZNjGHaQIWwflSGXA9NU3-1_c59KdWybcGsfcwZQE8e1lGGXAWw0EG_ffPNQR8e4cSGblMNQT-ZbCjZXpvNUhaE_5dbnnCF5oVCl7ANd29odZP_ZBtjAc5IlN7H6uiOilQfYO8nBg1Vqvvis6X9fcS3I-YNKOKsbM2gjjPr2YAnDpZTq8f3r9TTovceqe4c5zHnvaYmsfySw7niEsl3i6TRxJ3PjCcaV8LnqbSEKdbQyVCi-IvMIVT8sAIm0AY3hQh96gFwEWg-sOUJHh8yLZp2GuZzp8JFkppQVuPwUp7v3IZ74Je5..&amp;spm=a1z10.5-c.w4002-25832238778.44.78ba4bc7SHWlGR</x:v>
+      </x:c>
+      <x:c r="M38" t="str">
+        <x:v>Module, Collage, Diagram, AI/Psd</x:v>
+      </x:c>
+      <x:c r="N38" t="str">
+        <x:v>拼贴风分析图</x:v>
+      </x:c>
+      <x:c r="O38" t="str">
+        <x:v>拼贴感前期分析模版，适合图文混排、概念推演和作品集表达。</x:v>
+      </x:c>
+      <x:c r="P38" t="str">
+        <x:v>PNG / PDF / AI</x:v>
+      </x:c>
+      <x:c r="Q38" t="str">
+        <x:v>景观/建筑/环艺设计、作品集、分析图</x:v>
+      </x:c>
+      <x:c r="R38" t="str">
+        <x:v>新增 product37；图片已转 WebP 并接入网站。</x:v>
+      </x:c>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="1"/>
+      <x:c r="A39" s="1" t="str">
+        <x:v>P038</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>时间线分析模版</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>product38</x:v>
+      </x:c>
+      <x:c r="D39" t="str">
+        <x:v>Module Diagrams</x:v>
+      </x:c>
+      <x:c r="E39" t="str">
+        <x:v>01-cover.webp</x:v>
+      </x:c>
+      <x:c r="F39" t="str">
+        <x:v>02-detail-01.webp</x:v>
+      </x:c>
+      <x:c r="G39" t="str">
+        <x:v>03-detail-02.webp</x:v>
+      </x:c>
+      <x:c r="H39" t="str">
+        <x:v>04-detail-03.webp</x:v>
+      </x:c>
+      <x:c r="I39" t="str">
+        <x:v>05-detail-04.webp</x:v>
+      </x:c>
+      <x:c r="J39"/>
+      <x:c r="K39" t="n">
+        <x:v>12.8</x:v>
+      </x:c>
+      <x:c r="L39" t="str">
+        <x:v>https://item.taobao.com/item.htm?id=1031440595930&amp;pisk=gNRb9DMFfhdPSRuxXouzR261c-1M54lEMP_9-FF4WsCYyFQCWZIOuZWTyFbHuoRNXR_O7HQTM1SqwC_wc5JVBFQO13KZoi8tmhO12h00_qA2fOLV4hPwuC9u1eYMgqfZos8cs1nEYXleoEfipIVo0INRyZY86lexU_hfmrYmYXleoEfG6DoeQVt9Ta7U61eADa355wPO6GFxPgQ1-GFvX13SPNQ3M-CT6uQR-ZCOk1IAwaQhW-UAk-IJygbO6GKO641RqNCOXhC9tDFfzqsklVxF90qgvjLVV5F9NaIGvntlrad5ltOttcP_1VbfhMLA2mu3ViB6ctOrGkbXee_ClLgTeiLyGF_XFVeRDFLHtpSz2DS3h5e6aGNOP-0SPR2My85Y_4lnulWAraoZP4weStQlPMuSPR2GHabrb4g7LFf..&amp;spm=a1z10.5-c.w4002-25832238778.41.59a84bc75YXa5y</x:v>
+      </x:c>
+      <x:c r="M39" t="str">
+        <x:v>Module, Timeline, Diagram, AI/Psd</x:v>
+      </x:c>
+      <x:c r="N39" t="str">
+        <x:v>时间线分析图</x:v>
+      </x:c>
+      <x:c r="O39" t="str">
+        <x:v>时间线分析模版，适合阶段梳理、流程表达和作品集逻辑展示。</x:v>
+      </x:c>
+      <x:c r="P39" t="str">
+        <x:v>PNG / PDF / AI</x:v>
+      </x:c>
+      <x:c r="Q39" t="str">
+        <x:v>景观/建筑/环艺设计、作品集、时间线分析图</x:v>
+      </x:c>
+      <x:c r="R39" t="str">
+        <x:v>新增 product38；图片已转 WebP 并接入网站。</x:v>
+      </x:c>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="1"/>
+      <x:c r="A40" s="1" t="str">
+        <x:v>P039</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>自然教育模块素材</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>product39</x:v>
+      </x:c>
+      <x:c r="D40" t="str">
+        <x:v>Module Diagrams</x:v>
+      </x:c>
+      <x:c r="E40" t="str">
+        <x:v>01-cover.webp</x:v>
+      </x:c>
+      <x:c r="F40" t="str">
+        <x:v>02-detail-01.webp</x:v>
+      </x:c>
+      <x:c r="G40" t="str">
+        <x:v>03-detail-02.webp</x:v>
+      </x:c>
+      <x:c r="H40" t="str">
+        <x:v>04-detail-03.webp</x:v>
+      </x:c>
+      <x:c r="I40" t="str">
+        <x:v>05-detail-04.webp</x:v>
+      </x:c>
+      <x:c r="J40" t="str">
+        <x:v>06-detail-05.webp</x:v>
+      </x:c>
+      <x:c r="K40" t="n">
+        <x:v>15.8</x:v>
+      </x:c>
+      <x:c r="L40" t="str">
+        <x:v>https://item.taobao.com/item.htm?id=938231184689&amp;pisk=h6Pt5TZbtPAdGjQheaF0tuljwwjl1S0jlrz2lcG6Gr9IuqnXIVDDRrg7XhqmcZujOuuD1mmMCShQjzwilrimMoEYDcDfbfVYvoZviRVisx1jvlOmIACu7fqG-LqxCjtBOyu25CNuGN1Egjslq_fu7PrtqNb9lqgCJV02cjMjl2_KzVGX1xO_RDiEljibcAMBdq3scnOXCe_KSq-jlcMsOegrrnT_cj_KR4iIcjM_cy_KuDifPAH1SpVRp-bxV3va5DdJ8WI-CdzOkIdjXQ0oVQmdja-KfxEtBWf94VeQy43TpZ9IfyVTkVedlpi_lzPzEHzQiwpf3JrTUkL5EWFtuzeuVL5LMgzu15Me_6jdq8PQaWtOksP_PWZLaBTdYT2U1REJ9ebdXkyZsoLfuSX-x844bebOviWs8RdP1k95ISnnJ0bnSKJqp9uKqwQp3Kks82nl-Vv23vBF.&amp;spm=a1z10.5-c.w4002-25832238778.21.6cd24bc7sjA0kT</x:v>
+      </x:c>
+      <x:c r="M40" t="str">
+        <x:v>Module, Nature Education, Diagram, AI/Psd</x:v>
+      </x:c>
+      <x:c r="N40" t="str">
+        <x:v>自然教育模块</x:v>
+      </x:c>
+      <x:c r="O40" t="str">
+        <x:v>自然教育主题模块素材，适合户外教育、自然观察和场地活动分析。</x:v>
+      </x:c>
+      <x:c r="P40" t="str">
+        <x:v>PNG / PDF / AI</x:v>
+      </x:c>
+      <x:c r="Q40" t="str">
+        <x:v>景观/建筑/环艺设计、自然教育、作品集模块</x:v>
+      </x:c>
+      <x:c r="R40" t="str">
+        <x:v>新增 product39；图片已转 WebP 并接入网站。</x:v>
+      </x:c>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="1"/>
+      <x:c r="A41" s="1" t="str">
+        <x:v>P040</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>高级感剖面素材</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>product40</x:v>
+      </x:c>
+      <x:c r="D41" t="str">
+        <x:v>Animal Assets</x:v>
+      </x:c>
+      <x:c r="E41" t="str">
+        <x:v>01-cover.webp</x:v>
+      </x:c>
+      <x:c r="F41" t="str">
+        <x:v>02-detail-01.webp</x:v>
+      </x:c>
+      <x:c r="G41"/>
+      <x:c r="H41"/>
+      <x:c r="I41"/>
+      <x:c r="J41"/>
+      <x:c r="K41" t="n">
+        <x:v>9.9</x:v>
+      </x:c>
+      <x:c r="L41" t="str">
+        <x:v>https://item.taobao.com/item.htm?id=937136658086&amp;pisk=hstn2YMgKLFwjA3TnrYkHS-H-Vnv_8vX3_ELzMRgQL6Aa9SPpu7PdLPepkKRQzvfE3BPTgCrbCBkpuHCzFXywCMSdMpPZQAO1HHCwvNkZLvhzQCJpMpCVEHyYlK3QOWJQyyF8neiLHIrMjnxDp9CVBLrerPz7O51KTyeaazNQ16cag5Fz5JNU15P4gRzbRWf3W5P8g5ZI9B7T95FUPrNdTPzzQSrId51UgWeagkMQ16PP49nFIIFLP0DVma84u-FVwDvKzEkPhWeIy9FsdpOGskhnLRrZuI2lCxluOouEOYDQQ1eL02lIEvwsZKT6HybzzPXCppzlVlKnLLhkCzxuhDMHBTWrkyk-qCHopS3UxKqt1vHJCqEi2MXdB8DAJiBm2d9ELpTTfcZN6tvxUUtvnKHvLDGMyXEDt_CDIWjIA42lwW1LmHiIza58O6GMADguE_FC9oA.&amp;spm=a1z10.5-c.w4002-25832238778.13.53b24bc7Peq6S7</x:v>
+      </x:c>
+      <x:c r="M41" t="str">
+        <x:v>People, Plant, Animal, Section</x:v>
+      </x:c>
+      <x:c r="N41" t="str">
+        <x:v>剖面素材</x:v>
+      </x:c>
+      <x:c r="O41" t="str">
+        <x:v>高级感剖面素材，包含人物、植物与动物场景元素，适合剖面表达和图面点缀。</x:v>
+      </x:c>
+      <x:c r="P41" t="str">
+        <x:v>PNG / AI</x:v>
+      </x:c>
+      <x:c r="Q41" t="str">
+        <x:v>景观/建筑/环艺设计、作品集、剖面与场景素材</x:v>
+      </x:c>
+      <x:c r="R41" t="str">
+        <x:v>新增 product40；图片已转 WebP 并接入网站。</x:v>
+      </x:c>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="1"/>
+      <x:c r="A42" s="1" t="str">
+        <x:v>P041</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>高级感作品集分析图模版</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>product41</x:v>
+      </x:c>
+      <x:c r="D42" t="str">
+        <x:v>Module Diagrams</x:v>
+      </x:c>
+      <x:c r="E42" t="str">
+        <x:v>01-cover.webp</x:v>
+      </x:c>
+      <x:c r="F42" t="str">
+        <x:v>02-detail-01.webp</x:v>
+      </x:c>
+      <x:c r="G42" t="str">
+        <x:v>03-detail-02.webp</x:v>
+      </x:c>
+      <x:c r="H42" t="str">
+        <x:v>04-detail-03.webp</x:v>
+      </x:c>
+      <x:c r="I42" t="str">
+        <x:v>05-detail-04.webp</x:v>
+      </x:c>
+      <x:c r="J42"/>
+      <x:c r="K42" t="n">
+        <x:v>12.8</x:v>
+      </x:c>
+      <x:c r="L42" t="str">
+        <x:v>https://item.taobao.com/item.htm?id=1038863288544&amp;pisk=h0gsWY4xL81znP42Y0QVI_yGSrzvBxy43jeY1J2OHrPx9yFmNGPVkrWplbHOkmy4XSZLMjQN6fr9lSHzgoQ2jPrblveE7RlaW-ajZYMaQoSZAsGod59yz1nO5uaT6-ETDIFLZ7krH9oisf40kLJyzU-fAUVJBiexHeeLsJFAkZHY9Xe3iSBTkRdI9JVYkNETHwhLMSbOWNHYJXFY6tIYBoCd97PRkrUxHeQLKSUY6xUvOXe3MZmnJLAnD-jm9DOVzlw-OubATIPTF8Zd0Hxhi5G01GFdWUwKbm3aJVppOy3sCVEIQnQ7JVMsWkMJLwMDYIQVfqz2BCGqwb3RqITpdjcIqXIDrqitdzuip9pyjU0x_f3VDI0MCvhiGk7px49ngVMLxgJpO4wtDArXW6J9b7c40xCNSmjm9MzOuB8k_trTtWJ2OBsrilF3O8RBOij0XWVe3BOC4jf..&amp;spm=a1z10.5-c.w4002-25832238778.20.30294bc7xK9S3x</x:v>
+      </x:c>
+      <x:c r="M42" t="str">
+        <x:v>Module, Portfolio, Diagram, AI/Psd</x:v>
+      </x:c>
+      <x:c r="N42" t="str">
+        <x:v>作品集分析图</x:v>
+      </x:c>
+      <x:c r="O42" t="str">
+        <x:v>高级感作品集分析图模版，适合版式整理、场地分析和设计叙事。</x:v>
+      </x:c>
+      <x:c r="P42" t="str">
+        <x:v>PNG / PDF / AI</x:v>
+      </x:c>
+      <x:c r="Q42" t="str">
+        <x:v>景观/建筑/环艺设计、作品集、分析图</x:v>
+      </x:c>
+      <x:c r="R42" t="str">
+        <x:v>新增 product41；图片已转 WebP 并接入网站。</x:v>
+      </x:c>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="1"/>
+      <x:c r="A43" s="1" t="str">
+        <x:v>P042</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>宠物友好设计素材</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>product42</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
+        <x:v>Animal Assets</x:v>
+      </x:c>
+      <x:c r="E43" t="str">
+        <x:v>01-cover.webp</x:v>
+      </x:c>
+      <x:c r="F43" t="str">
+        <x:v>02-detail-01.webp</x:v>
+      </x:c>
+      <x:c r="G43"/>
+      <x:c r="H43"/>
+      <x:c r="I43"/>
+      <x:c r="J43"/>
+      <x:c r="K43" t="n">
+        <x:v>8.8</x:v>
+      </x:c>
+      <x:c r="L43" t="str">
+        <x:v>https://item.taobao.com/item.htm?id=931639797310&amp;pisk=hQjreoAx6xJuNrtRR5WlEoNbh3BJG_mIAHO7osRcp6OWALxDndJrE0xnrZJhOseLe36HT65XMgwJO8hFT9Wy-6OCF36Jv43m-GSrmKvFnpmHrIpliat315Z_fTBJv__huUDnoKAvUpchte0DnIprZHAk-jXDKIAHxHfHimvHUXvkEUD03L9pE2AorjqDIppkt6x33EvHpHAhtU2VnIpHxBbRdD7xwMJnkcC2HDj2UEYfEWiehi26rC8mRQRl0lLPc1yBEpxhrT125aPZ4ZXlaNYGql39rTfPSFju4fdXWHzS6DmC1YNc0SbFuNI35qj0791NJ9gLsGa5Gt6Cjvg4WlSPVwIQq-V4awWp56roylaGih_h00MQZMO5gg7ZkzEcvsxlIiv23RpBg4BPeF8qJ2L8eKR_EU0KJUvv3Cw4323py8p218Yl.&amp;spm=a1z10.5-c.w4002-25832238778.46.22344bc7OJwFbL</x:v>
+      </x:c>
+      <x:c r="M43" t="str">
+        <x:v>Pet, Animal, Plant, PSD</x:v>
+      </x:c>
+      <x:c r="N43" t="str">
+        <x:v>宠物友好设计素材</x:v>
+      </x:c>
+      <x:c r="O43" t="str">
+        <x:v>宠物友好主题设计素材，适合宠物活动空间、社区场景和景观分析表达。</x:v>
+      </x:c>
+      <x:c r="P43" t="str">
+        <x:v>JPG / PSD</x:v>
+      </x:c>
+      <x:c r="Q43" t="str">
+        <x:v>景观/建筑/环艺设计、宠物友好空间、作品集素材</x:v>
+      </x:c>
+      <x:c r="R43" t="str">
+        <x:v>新增 product42；图片已转 WebP 并接入网站。</x:v>
+      </x:c>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="1"/>
+      <x:c r="A44" s="1" t="str">
+        <x:v>P043</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>人物分析模版素材</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>product43</x:v>
+      </x:c>
+      <x:c r="D44" t="str">
+        <x:v>Module Diagrams</x:v>
+      </x:c>
+      <x:c r="E44" t="str">
+        <x:v>01-cover.webp</x:v>
+      </x:c>
+      <x:c r="F44" t="str">
+        <x:v>02-detail-01.webp</x:v>
+      </x:c>
+      <x:c r="G44" t="str">
+        <x:v>03-detail-02.webp</x:v>
+      </x:c>
+      <x:c r="H44" t="str">
+        <x:v>04-detail-03.webp</x:v>
+      </x:c>
+      <x:c r="I44" t="str">
+        <x:v>05-detail-04.webp</x:v>
+      </x:c>
+      <x:c r="J44"/>
+      <x:c r="K44" t="n">
+        <x:v>12.8</x:v>
+      </x:c>
+      <x:c r="L44" t="str">
+        <x:v>https://item.taobao.com/item.htm?id=931080658689&amp;pisk=hbCZeHxK292LfJOOhu7ZpZrCgCQ9AGcjGIt_KM-hkit6GFAH-U8ZSfAmI98ccMUYWC_D0iSBv1a9cPnV0Z7wnitf5C_9MRChsF5ZtBYf-jciiHLGxOO0VuN7NNQ9MG6cL63mKexp7E0GmKDH-HLZmIxMnDbHoHxDiIjDxeYDkAcMmhbHKHLZsFAmiwDHPFDmmAjc-y89SIxcmd4F-HLDinb4AjWKXscHAqMqGezX7d-VGHPP56b6IsVRzjYCTtduWSxzTDxCoaBDLsk4ne5Nzs8d88kk817PgE5YDW-EW0hmGgg_x6rh39WRi8Mht87f4tQjHuf7CM_59BlQg72G3MsdFb43M_7CWBfL1VZbNwXlk1oaKR5ftLjlTxFYb97y1Cpy8ezJlHkO7NpyLxHvBPLeVPviHxpMJe-78ykxHdU983aMI&amp;spm=a1z10.5-c.w4002-25832238778.34.2d974bc7oGk63S</x:v>
+      </x:c>
+      <x:c r="M44" t="str">
+        <x:v>Module, People Analysis, Diagram, AI/Psd</x:v>
+      </x:c>
+      <x:c r="N44" t="str">
+        <x:v>人物分析模版</x:v>
+      </x:c>
+      <x:c r="O44" t="str">
+        <x:v>人物分析模版素材，适合人群行为、活动路径和空间使用分析。</x:v>
+      </x:c>
+      <x:c r="P44" t="str">
+        <x:v>PNG / PDF / AI</x:v>
+      </x:c>
+      <x:c r="Q44" t="str">
+        <x:v>景观/建筑/环艺设计、作品集、人物分析图</x:v>
+      </x:c>
+      <x:c r="R44" t="str">
+        <x:v>新增 product43；图片已转 WebP 并接入网站。</x:v>
+      </x:c>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" s="1"/>
+      <x:c r="A45" s="1" t="str">
+        <x:v>P044</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>景观建筑户外素材</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>product44</x:v>
+      </x:c>
+      <x:c r="D45" t="str">
+        <x:v>Animal Assets</x:v>
+      </x:c>
+      <x:c r="E45" t="str">
+        <x:v>01-cover.webp</x:v>
+      </x:c>
+      <x:c r="F45" t="str">
+        <x:v>02-detail-01.webp</x:v>
+      </x:c>
+      <x:c r="G45"/>
+      <x:c r="H45"/>
+      <x:c r="I45"/>
+      <x:c r="J45"/>
+      <x:c r="K45" t="n">
+        <x:v>9.9</x:v>
+      </x:c>
+      <x:c r="L45" t="str">
+        <x:v>https://item.taobao.com/item.htm?id=1055977071131&amp;mi_id=00001syYEMR9R4lWeu08AGF3BwgY1oe1l1g7zpFGqkdklOQ&amp;spm=a21xtw.29178619.0.0&amp;xxc=shop</x:v>
+      </x:c>
+      <x:c r="M45" t="str">
+        <x:v>People, Plant, Animal, Outdoor</x:v>
+      </x:c>
+      <x:c r="N45" t="str">
+        <x:v>户外素材</x:v>
+      </x:c>
+      <x:c r="O45" t="str">
+        <x:v>景观建筑户外素材，包含人物、植物与动物场景元素，适合户外空间氛围表达。</x:v>
+      </x:c>
+      <x:c r="P45" t="str">
+        <x:v>PNG / AI</x:v>
+      </x:c>
+      <x:c r="Q45" t="str">
+        <x:v>景观/建筑/环艺设计、户外场景、作品集素材</x:v>
+      </x:c>
+      <x:c r="R45" t="str">
+        <x:v>新增 product44；图片已转 WebP 并接入网站。</x:v>
+      </x:c>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" s="1"/>
+      <x:c r="A46" s="1" t="str">
+        <x:v>P045</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>景观建筑户外设计模块</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>product45</x:v>
+      </x:c>
+      <x:c r="D46" t="str">
+        <x:v>Module Diagrams</x:v>
+      </x:c>
+      <x:c r="E46" t="str">
+        <x:v>01-cover.webp</x:v>
+      </x:c>
+      <x:c r="F46" t="str">
+        <x:v>02-detail-01.webp</x:v>
+      </x:c>
+      <x:c r="G46" t="str">
+        <x:v>03-detail-02.webp</x:v>
+      </x:c>
+      <x:c r="H46" t="str">
+        <x:v>04-detail-03.webp</x:v>
+      </x:c>
+      <x:c r="I46" t="str">
+        <x:v>05-detail-04.webp</x:v>
+      </x:c>
+      <x:c r="J46" t="str">
+        <x:v>06-detail-05.webp</x:v>
+      </x:c>
+      <x:c r="K46" t="n">
+        <x:v>14.8</x:v>
+      </x:c>
+      <x:c r="L46" t="str">
+        <x:v>https://item.taobao.com/item.htm?id=1055979771498&amp;mi_id=0000ouFvbhSAsCbAQxlOUNefWmkO3e8o61iM_BWMq4r4yCQ&amp;spm=a21xtw.29178619.0.0&amp;xxc=shop</x:v>
+      </x:c>
+      <x:c r="M46" t="str">
+        <x:v>Module, Outdoor, Landscape, AI/Psd</x:v>
+      </x:c>
+      <x:c r="N46" t="str">
+        <x:v>户外设计模块</x:v>
+      </x:c>
+      <x:c r="O46" t="str">
+        <x:v>景观建筑户外设计模块，适合节点设计、活动场景和作品集模块表达。</x:v>
+      </x:c>
+      <x:c r="P46" t="str">
+        <x:v>PNG / PDF / AI</x:v>
+      </x:c>
+      <x:c r="Q46" t="str">
+        <x:v>景观/建筑/环艺设计、作品集、户外节点模块</x:v>
+      </x:c>
+      <x:c r="R46" t="str">
+        <x:v>新增 product45；图片已转 WebP 并接入网站。 另有 07-detail-06.webp ～ 15-detail-14.webp，已接入网站 images 列表。</x:v>
+      </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="1"/>
@@ -5464,34 +6239,34 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15">
-      <x:c r="A1" s="9" t="s">
+      <x:c r="A1" s="48" t="s">
         <x:v>461</x:v>
       </x:c>
-      <x:c r="B1" s="9" t="s">
+      <x:c r="B1" s="48" t="s">
         <x:v>462</x:v>
       </x:c>
-      <x:c r="C1" s="9" t="s">
+      <x:c r="C1" s="48" t="s">
         <x:v>463</x:v>
       </x:c>
-      <x:c r="D1" s="9" t="s">
+      <x:c r="D1" s="48" t="s">
         <x:v>464</x:v>
       </x:c>
-      <x:c r="E1" s="9" t="s">
+      <x:c r="E1" s="48" t="s">
         <x:v>465</x:v>
       </x:c>
-      <x:c r="F1" s="9" t="s">
+      <x:c r="F1" s="48" t="s">
         <x:v>466</x:v>
       </x:c>
-      <x:c r="G1" s="9" t="s">
+      <x:c r="G1" s="48" t="s">
         <x:v>467</x:v>
       </x:c>
-      <x:c r="H1" s="9" t="s">
+      <x:c r="H1" s="48" t="s">
         <x:v>468</x:v>
       </x:c>
-      <x:c r="I1" s="9" t="s">
+      <x:c r="I1" s="48" t="s">
         <x:v>289</x:v>
       </x:c>
-      <x:c r="J1" s="9" t="s">
+      <x:c r="J1" s="48" t="s">
         <x:v>469</x:v>
       </x:c>
     </x:row>
@@ -10356,6 +11131,2054 @@
         <x:v>images/products/product30/10-detail-09.webp</x:v>
       </x:c>
       <x:c r="J153" s="28" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" t="n">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="B154" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C154" t="str">
+        <x:v>product31</x:v>
+      </x:c>
+      <x:c r="D154" t="str">
+        <x:v>商品封面</x:v>
+      </x:c>
+      <x:c r="E154" t="str">
+        <x:v>product31/截屏2026-06-08 下午3.35.46.png</x:v>
+      </x:c>
+      <x:c r="F154" t="str">
+        <x:v>截屏2026-06-08 下午3.35.46.png</x:v>
+      </x:c>
+      <x:c r="G154" t="n">
+        <x:v>1780</x:v>
+      </x:c>
+      <x:c r="H154" t="n">
+        <x:v>1258</x:v>
+      </x:c>
+      <x:c r="I154" t="str">
+        <x:v>images/products/product31/01-cover.webp</x:v>
+      </x:c>
+      <x:c r="J154" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" t="n">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="B155" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C155" t="str">
+        <x:v>product31</x:v>
+      </x:c>
+      <x:c r="D155" t="str">
+        <x:v>商品详情图1</x:v>
+      </x:c>
+      <x:c r="E155" t="str">
+        <x:v>product31/截屏2026-06-08 下午3.35.27.png</x:v>
+      </x:c>
+      <x:c r="F155" t="str">
+        <x:v>截屏2026-06-08 下午3.35.27.png</x:v>
+      </x:c>
+      <x:c r="G155" t="n">
+        <x:v>1778</x:v>
+      </x:c>
+      <x:c r="H155" t="n">
+        <x:v>1254</x:v>
+      </x:c>
+      <x:c r="I155" t="str">
+        <x:v>images/products/product31/02-detail-01.webp</x:v>
+      </x:c>
+      <x:c r="J155" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" t="n">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="B156" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C156" t="str">
+        <x:v>product32</x:v>
+      </x:c>
+      <x:c r="D156" t="str">
+        <x:v>商品封面</x:v>
+      </x:c>
+      <x:c r="E156" t="str">
+        <x:v>product32/截屏2026-06-08 下午3.43.06.png</x:v>
+      </x:c>
+      <x:c r="F156" t="str">
+        <x:v>截屏2026-06-08 下午3.43.06.png</x:v>
+      </x:c>
+      <x:c r="G156" t="n">
+        <x:v>1524</x:v>
+      </x:c>
+      <x:c r="H156" t="n">
+        <x:v>1528</x:v>
+      </x:c>
+      <x:c r="I156" t="str">
+        <x:v>images/products/product32/01-cover.webp</x:v>
+      </x:c>
+      <x:c r="J156" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" t="n">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="B157" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C157" t="str">
+        <x:v>product33</x:v>
+      </x:c>
+      <x:c r="D157" t="str">
+        <x:v>商品封面</x:v>
+      </x:c>
+      <x:c r="E157" t="str">
+        <x:v>product33/截屏2026-06-08 下午4.07.02.png</x:v>
+      </x:c>
+      <x:c r="F157" t="str">
+        <x:v>截屏2026-06-08 下午4.07.02.png</x:v>
+      </x:c>
+      <x:c r="G157" t="n">
+        <x:v>1810</x:v>
+      </x:c>
+      <x:c r="H157" t="n">
+        <x:v>1274</x:v>
+      </x:c>
+      <x:c r="I157" t="str">
+        <x:v>images/products/product33/01-cover.webp</x:v>
+      </x:c>
+      <x:c r="J157" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" t="n">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="B158" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C158" t="str">
+        <x:v>product33</x:v>
+      </x:c>
+      <x:c r="D158" t="str">
+        <x:v>商品详情图1</x:v>
+      </x:c>
+      <x:c r="E158" t="str">
+        <x:v>product33/截屏2026-06-08 下午4.07.13.png</x:v>
+      </x:c>
+      <x:c r="F158" t="str">
+        <x:v>截屏2026-06-08 下午4.07.13.png</x:v>
+      </x:c>
+      <x:c r="G158" t="n">
+        <x:v>1808</x:v>
+      </x:c>
+      <x:c r="H158" t="n">
+        <x:v>1276</x:v>
+      </x:c>
+      <x:c r="I158" t="str">
+        <x:v>images/products/product33/02-detail-01.webp</x:v>
+      </x:c>
+      <x:c r="J158" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" t="n">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="B159" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C159" t="str">
+        <x:v>product33</x:v>
+      </x:c>
+      <x:c r="D159" t="str">
+        <x:v>商品详情图2</x:v>
+      </x:c>
+      <x:c r="E159" t="str">
+        <x:v>product33/截屏2026-06-08 下午4.06.38.png</x:v>
+      </x:c>
+      <x:c r="F159" t="str">
+        <x:v>截屏2026-06-08 下午4.06.38.png</x:v>
+      </x:c>
+      <x:c r="G159" t="n">
+        <x:v>1806</x:v>
+      </x:c>
+      <x:c r="H159" t="n">
+        <x:v>1272</x:v>
+      </x:c>
+      <x:c r="I159" t="str">
+        <x:v>images/products/product33/03-detail-02.webp</x:v>
+      </x:c>
+      <x:c r="J159" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" t="n">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="B160" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C160" t="str">
+        <x:v>product33</x:v>
+      </x:c>
+      <x:c r="D160" t="str">
+        <x:v>商品详情图3</x:v>
+      </x:c>
+      <x:c r="E160" t="str">
+        <x:v>product33/截屏2026-06-08 下午4.06.48.png</x:v>
+      </x:c>
+      <x:c r="F160" t="str">
+        <x:v>截屏2026-06-08 下午4.06.48.png</x:v>
+      </x:c>
+      <x:c r="G160" t="n">
+        <x:v>1806</x:v>
+      </x:c>
+      <x:c r="H160" t="n">
+        <x:v>1274</x:v>
+      </x:c>
+      <x:c r="I160" t="str">
+        <x:v>images/products/product33/04-detail-03.webp</x:v>
+      </x:c>
+      <x:c r="J160" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="B161" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C161" t="str">
+        <x:v>product33</x:v>
+      </x:c>
+      <x:c r="D161" t="str">
+        <x:v>商品详情图4</x:v>
+      </x:c>
+      <x:c r="E161" t="str">
+        <x:v>product33/截屏2026-06-08 下午4.07.24.png</x:v>
+      </x:c>
+      <x:c r="F161" t="str">
+        <x:v>截屏2026-06-08 下午4.07.24.png</x:v>
+      </x:c>
+      <x:c r="G161" t="n">
+        <x:v>1806</x:v>
+      </x:c>
+      <x:c r="H161" t="n">
+        <x:v>1278</x:v>
+      </x:c>
+      <x:c r="I161" t="str">
+        <x:v>images/products/product33/05-detail-04.webp</x:v>
+      </x:c>
+      <x:c r="J161" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" t="n">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="B162" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C162" t="str">
+        <x:v>product34</x:v>
+      </x:c>
+      <x:c r="D162" t="str">
+        <x:v>商品封面</x:v>
+      </x:c>
+      <x:c r="E162" t="str">
+        <x:v>product34/截屏2026-06-08 下午4.09.53.png</x:v>
+      </x:c>
+      <x:c r="F162" t="str">
+        <x:v>截屏2026-06-08 下午4.09.53.png</x:v>
+      </x:c>
+      <x:c r="G162" t="n">
+        <x:v>1256</x:v>
+      </x:c>
+      <x:c r="H162" t="n">
+        <x:v>1254</x:v>
+      </x:c>
+      <x:c r="I162" t="str">
+        <x:v>images/products/product34/01-cover.webp</x:v>
+      </x:c>
+      <x:c r="J162" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" t="n">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="B163" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C163" t="str">
+        <x:v>product34</x:v>
+      </x:c>
+      <x:c r="D163" t="str">
+        <x:v>商品详情图1</x:v>
+      </x:c>
+      <x:c r="E163" t="str">
+        <x:v>product34/截屏2026-06-08 下午4.10.28.png</x:v>
+      </x:c>
+      <x:c r="F163" t="str">
+        <x:v>截屏2026-06-08 下午4.10.28.png</x:v>
+      </x:c>
+      <x:c r="G163" t="n">
+        <x:v>1072</x:v>
+      </x:c>
+      <x:c r="H163" t="n">
+        <x:v>1252</x:v>
+      </x:c>
+      <x:c r="I163" t="str">
+        <x:v>images/products/product34/02-detail-01.webp</x:v>
+      </x:c>
+      <x:c r="J163" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164" t="n">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="B164" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C164" t="str">
+        <x:v>product35</x:v>
+      </x:c>
+      <x:c r="D164" t="str">
+        <x:v>商品封面</x:v>
+      </x:c>
+      <x:c r="E164" t="str">
+        <x:v>product35/截屏2026-06-08 下午4.16.47.png</x:v>
+      </x:c>
+      <x:c r="F164" t="str">
+        <x:v>截屏2026-06-08 下午4.16.47.png</x:v>
+      </x:c>
+      <x:c r="G164" t="n">
+        <x:v>1778</x:v>
+      </x:c>
+      <x:c r="H164" t="n">
+        <x:v>1256</x:v>
+      </x:c>
+      <x:c r="I164" t="str">
+        <x:v>images/products/product35/01-cover.webp</x:v>
+      </x:c>
+      <x:c r="J164" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165" t="n">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="B165" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C165" t="str">
+        <x:v>product35</x:v>
+      </x:c>
+      <x:c r="D165" t="str">
+        <x:v>商品详情图1</x:v>
+      </x:c>
+      <x:c r="E165" t="str">
+        <x:v>product35/截屏2026-06-08 下午4.17.09.png</x:v>
+      </x:c>
+      <x:c r="F165" t="str">
+        <x:v>截屏2026-06-08 下午4.17.09.png</x:v>
+      </x:c>
+      <x:c r="G165" t="n">
+        <x:v>1774</x:v>
+      </x:c>
+      <x:c r="H165" t="n">
+        <x:v>1254</x:v>
+      </x:c>
+      <x:c r="I165" t="str">
+        <x:v>images/products/product35/02-detail-01.webp</x:v>
+      </x:c>
+      <x:c r="J165" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166" t="n">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="B166" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C166" t="str">
+        <x:v>product36</x:v>
+      </x:c>
+      <x:c r="D166" t="str">
+        <x:v>商品封面</x:v>
+      </x:c>
+      <x:c r="E166" t="str">
+        <x:v>product36/截屏2026-06-08 下午4.32.55.png</x:v>
+      </x:c>
+      <x:c r="F166" t="str">
+        <x:v>截屏2026-06-08 下午4.32.55.png</x:v>
+      </x:c>
+      <x:c r="G166" t="n">
+        <x:v>1780</x:v>
+      </x:c>
+      <x:c r="H166" t="n">
+        <x:v>1256</x:v>
+      </x:c>
+      <x:c r="I166" t="str">
+        <x:v>images/products/product36/01-cover.webp</x:v>
+      </x:c>
+      <x:c r="J166" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167" t="n">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="B167" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C167" t="str">
+        <x:v>product36</x:v>
+      </x:c>
+      <x:c r="D167" t="str">
+        <x:v>商品详情图1</x:v>
+      </x:c>
+      <x:c r="E167" t="str">
+        <x:v>product36/截屏2026-06-08 下午4.33.14.png</x:v>
+      </x:c>
+      <x:c r="F167" t="str">
+        <x:v>截屏2026-06-08 下午4.33.14.png</x:v>
+      </x:c>
+      <x:c r="G167" t="n">
+        <x:v>1780</x:v>
+      </x:c>
+      <x:c r="H167" t="n">
+        <x:v>1254</x:v>
+      </x:c>
+      <x:c r="I167" t="str">
+        <x:v>images/products/product36/02-detail-01.webp</x:v>
+      </x:c>
+      <x:c r="J167" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168" t="n">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="B168" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C168" t="str">
+        <x:v>product36</x:v>
+      </x:c>
+      <x:c r="D168" t="str">
+        <x:v>商品详情图2</x:v>
+      </x:c>
+      <x:c r="E168" t="str">
+        <x:v>product36/截屏2026-06-08 下午4.32.35.png</x:v>
+      </x:c>
+      <x:c r="F168" t="str">
+        <x:v>截屏2026-06-08 下午4.32.35.png</x:v>
+      </x:c>
+      <x:c r="G168" t="n">
+        <x:v>1780</x:v>
+      </x:c>
+      <x:c r="H168" t="n">
+        <x:v>1256</x:v>
+      </x:c>
+      <x:c r="I168" t="str">
+        <x:v>images/products/product36/03-detail-02.webp</x:v>
+      </x:c>
+      <x:c r="J168" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169" t="n">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="B169" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C169" t="str">
+        <x:v>product36</x:v>
+      </x:c>
+      <x:c r="D169" t="str">
+        <x:v>商品详情图3</x:v>
+      </x:c>
+      <x:c r="E169" t="str">
+        <x:v>product36/截屏2026-06-08 下午4.34.40.png</x:v>
+      </x:c>
+      <x:c r="F169" t="str">
+        <x:v>截屏2026-06-08 下午4.34.40.png</x:v>
+      </x:c>
+      <x:c r="G169" t="n">
+        <x:v>1780</x:v>
+      </x:c>
+      <x:c r="H169" t="n">
+        <x:v>1260</x:v>
+      </x:c>
+      <x:c r="I169" t="str">
+        <x:v>images/products/product36/04-detail-03.webp</x:v>
+      </x:c>
+      <x:c r="J169" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170">
+      <x:c r="A170" t="n">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="B170" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C170" t="str">
+        <x:v>product36</x:v>
+      </x:c>
+      <x:c r="D170" t="str">
+        <x:v>商品详情图4</x:v>
+      </x:c>
+      <x:c r="E170" t="str">
+        <x:v>product36/截屏2026-06-08 下午4.32.15.png</x:v>
+      </x:c>
+      <x:c r="F170" t="str">
+        <x:v>截屏2026-06-08 下午4.32.15.png</x:v>
+      </x:c>
+      <x:c r="G170" t="n">
+        <x:v>1780</x:v>
+      </x:c>
+      <x:c r="H170" t="n">
+        <x:v>1256</x:v>
+      </x:c>
+      <x:c r="I170" t="str">
+        <x:v>images/products/product36/05-detail-04.webp</x:v>
+      </x:c>
+      <x:c r="J170" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171" t="n">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="B171" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C171" t="str">
+        <x:v>product37</x:v>
+      </x:c>
+      <x:c r="D171" t="str">
+        <x:v>商品封面</x:v>
+      </x:c>
+      <x:c r="E171" t="str">
+        <x:v>product37/截屏2026-06-08 下午4.31.11.png</x:v>
+      </x:c>
+      <x:c r="F171" t="str">
+        <x:v>截屏2026-06-08 下午4.31.11.png</x:v>
+      </x:c>
+      <x:c r="G171" t="n">
+        <x:v>1780</x:v>
+      </x:c>
+      <x:c r="H171" t="n">
+        <x:v>1260</x:v>
+      </x:c>
+      <x:c r="I171" t="str">
+        <x:v>images/products/product37/01-cover.webp</x:v>
+      </x:c>
+      <x:c r="J171" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172">
+      <x:c r="A172" t="n">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="B172" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C172" t="str">
+        <x:v>product37</x:v>
+      </x:c>
+      <x:c r="D172" t="str">
+        <x:v>商品详情图1</x:v>
+      </x:c>
+      <x:c r="E172" t="str">
+        <x:v>product37/截屏2026-06-08 下午4.29.16.png</x:v>
+      </x:c>
+      <x:c r="F172" t="str">
+        <x:v>截屏2026-06-08 下午4.29.16.png</x:v>
+      </x:c>
+      <x:c r="G172" t="n">
+        <x:v>1778</x:v>
+      </x:c>
+      <x:c r="H172" t="n">
+        <x:v>1252</x:v>
+      </x:c>
+      <x:c r="I172" t="str">
+        <x:v>images/products/product37/02-detail-01.webp</x:v>
+      </x:c>
+      <x:c r="J172" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173">
+      <x:c r="A173" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="B173" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C173" t="str">
+        <x:v>product37</x:v>
+      </x:c>
+      <x:c r="D173" t="str">
+        <x:v>商品详情图2</x:v>
+      </x:c>
+      <x:c r="E173" t="str">
+        <x:v>product37/截屏2026-06-08 下午4.27.30.png</x:v>
+      </x:c>
+      <x:c r="F173" t="str">
+        <x:v>截屏2026-06-08 下午4.27.30.png</x:v>
+      </x:c>
+      <x:c r="G173" t="n">
+        <x:v>1780</x:v>
+      </x:c>
+      <x:c r="H173" t="n">
+        <x:v>1258</x:v>
+      </x:c>
+      <x:c r="I173" t="str">
+        <x:v>images/products/product37/03-detail-02.webp</x:v>
+      </x:c>
+      <x:c r="J173" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174">
+      <x:c r="A174" t="n">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="B174" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C174" t="str">
+        <x:v>product37</x:v>
+      </x:c>
+      <x:c r="D174" t="str">
+        <x:v>商品详情图3</x:v>
+      </x:c>
+      <x:c r="E174" t="str">
+        <x:v>product37/截屏2026-06-08 下午4.28.59.png</x:v>
+      </x:c>
+      <x:c r="F174" t="str">
+        <x:v>截屏2026-06-08 下午4.28.59.png</x:v>
+      </x:c>
+      <x:c r="G174" t="n">
+        <x:v>1780</x:v>
+      </x:c>
+      <x:c r="H174" t="n">
+        <x:v>1258</x:v>
+      </x:c>
+      <x:c r="I174" t="str">
+        <x:v>images/products/product37/04-detail-03.webp</x:v>
+      </x:c>
+      <x:c r="J174" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175">
+      <x:c r="A175" t="n">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="B175" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C175" t="str">
+        <x:v>product37</x:v>
+      </x:c>
+      <x:c r="D175" t="str">
+        <x:v>商品详情图4</x:v>
+      </x:c>
+      <x:c r="E175" t="str">
+        <x:v>product37/截屏2026-06-08 下午4.29.40.png</x:v>
+      </x:c>
+      <x:c r="F175" t="str">
+        <x:v>截屏2026-06-08 下午4.29.40.png</x:v>
+      </x:c>
+      <x:c r="G175" t="n">
+        <x:v>1780</x:v>
+      </x:c>
+      <x:c r="H175" t="n">
+        <x:v>1258</x:v>
+      </x:c>
+      <x:c r="I175" t="str">
+        <x:v>images/products/product37/05-detail-04.webp</x:v>
+      </x:c>
+      <x:c r="J175" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176">
+      <x:c r="A176" t="n">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="B176" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C176" t="str">
+        <x:v>product38</x:v>
+      </x:c>
+      <x:c r="D176" t="str">
+        <x:v>商品封面</x:v>
+      </x:c>
+      <x:c r="E176" t="str">
+        <x:v>product38/截屏2026-06-08 下午4.38.36.png</x:v>
+      </x:c>
+      <x:c r="F176" t="str">
+        <x:v>截屏2026-06-08 下午4.38.36.png</x:v>
+      </x:c>
+      <x:c r="G176" t="n">
+        <x:v>1780</x:v>
+      </x:c>
+      <x:c r="H176" t="n">
+        <x:v>1254</x:v>
+      </x:c>
+      <x:c r="I176" t="str">
+        <x:v>images/products/product38/01-cover.webp</x:v>
+      </x:c>
+      <x:c r="J176" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177">
+      <x:c r="A177" t="n">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="B177" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C177" t="str">
+        <x:v>product38</x:v>
+      </x:c>
+      <x:c r="D177" t="str">
+        <x:v>商品详情图1</x:v>
+      </x:c>
+      <x:c r="E177" t="str">
+        <x:v>product38/截屏2026-06-08 下午4.40.54.png</x:v>
+      </x:c>
+      <x:c r="F177" t="str">
+        <x:v>截屏2026-06-08 下午4.40.54.png</x:v>
+      </x:c>
+      <x:c r="G177" t="n">
+        <x:v>1780</x:v>
+      </x:c>
+      <x:c r="H177" t="n">
+        <x:v>1258</x:v>
+      </x:c>
+      <x:c r="I177" t="str">
+        <x:v>images/products/product38/02-detail-01.webp</x:v>
+      </x:c>
+      <x:c r="J177" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178">
+      <x:c r="A178" t="n">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="B178" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C178" t="str">
+        <x:v>product38</x:v>
+      </x:c>
+      <x:c r="D178" t="str">
+        <x:v>商品详情图2</x:v>
+      </x:c>
+      <x:c r="E178" t="str">
+        <x:v>product38/截屏2026-06-08 下午4.42.40.png</x:v>
+      </x:c>
+      <x:c r="F178" t="str">
+        <x:v>截屏2026-06-08 下午4.42.40.png</x:v>
+      </x:c>
+      <x:c r="G178" t="n">
+        <x:v>1778</x:v>
+      </x:c>
+      <x:c r="H178" t="n">
+        <x:v>1256</x:v>
+      </x:c>
+      <x:c r="I178" t="str">
+        <x:v>images/products/product38/03-detail-02.webp</x:v>
+      </x:c>
+      <x:c r="J178" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179">
+      <x:c r="A179" t="n">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="B179" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C179" t="str">
+        <x:v>product38</x:v>
+      </x:c>
+      <x:c r="D179" t="str">
+        <x:v>商品详情图3</x:v>
+      </x:c>
+      <x:c r="E179" t="str">
+        <x:v>product38/截屏2026-06-08 下午4.41.12.png</x:v>
+      </x:c>
+      <x:c r="F179" t="str">
+        <x:v>截屏2026-06-08 下午4.41.12.png</x:v>
+      </x:c>
+      <x:c r="G179" t="n">
+        <x:v>1778</x:v>
+      </x:c>
+      <x:c r="H179" t="n">
+        <x:v>1258</x:v>
+      </x:c>
+      <x:c r="I179" t="str">
+        <x:v>images/products/product38/04-detail-03.webp</x:v>
+      </x:c>
+      <x:c r="J179" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180">
+      <x:c r="A180" t="n">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="B180" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C180" t="str">
+        <x:v>product38</x:v>
+      </x:c>
+      <x:c r="D180" t="str">
+        <x:v>商品详情图4</x:v>
+      </x:c>
+      <x:c r="E180" t="str">
+        <x:v>product38/截屏2026-06-08 下午4.40.31.png</x:v>
+      </x:c>
+      <x:c r="F180" t="str">
+        <x:v>截屏2026-06-08 下午4.40.31.png</x:v>
+      </x:c>
+      <x:c r="G180" t="n">
+        <x:v>1782</x:v>
+      </x:c>
+      <x:c r="H180" t="n">
+        <x:v>1258</x:v>
+      </x:c>
+      <x:c r="I180" t="str">
+        <x:v>images/products/product38/05-detail-04.webp</x:v>
+      </x:c>
+      <x:c r="J180" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181">
+      <x:c r="A181" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="B181" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C181" t="str">
+        <x:v>product39</x:v>
+      </x:c>
+      <x:c r="D181" t="str">
+        <x:v>商品封面</x:v>
+      </x:c>
+      <x:c r="E181" t="str">
+        <x:v>product39/截屏2026-06-08 下午4.46.16.png</x:v>
+      </x:c>
+      <x:c r="F181" t="str">
+        <x:v>截屏2026-06-08 下午4.46.16.png</x:v>
+      </x:c>
+      <x:c r="G181" t="n">
+        <x:v>1774</x:v>
+      </x:c>
+      <x:c r="H181" t="n">
+        <x:v>1254</x:v>
+      </x:c>
+      <x:c r="I181" t="str">
+        <x:v>images/products/product39/01-cover.webp</x:v>
+      </x:c>
+      <x:c r="J181" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182">
+      <x:c r="A182" t="n">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="B182" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C182" t="str">
+        <x:v>product39</x:v>
+      </x:c>
+      <x:c r="D182" t="str">
+        <x:v>商品详情图1</x:v>
+      </x:c>
+      <x:c r="E182" t="str">
+        <x:v>product39/截屏2026-06-08 下午4.47.40.png</x:v>
+      </x:c>
+      <x:c r="F182" t="str">
+        <x:v>截屏2026-06-08 下午4.47.40.png</x:v>
+      </x:c>
+      <x:c r="G182" t="n">
+        <x:v>1778</x:v>
+      </x:c>
+      <x:c r="H182" t="n">
+        <x:v>1258</x:v>
+      </x:c>
+      <x:c r="I182" t="str">
+        <x:v>images/products/product39/02-detail-01.webp</x:v>
+      </x:c>
+      <x:c r="J182" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183" t="n">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="B183" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C183" t="str">
+        <x:v>product39</x:v>
+      </x:c>
+      <x:c r="D183" t="str">
+        <x:v>商品详情图2</x:v>
+      </x:c>
+      <x:c r="E183" t="str">
+        <x:v>product39/截屏2026-06-08 下午4.49.43.png</x:v>
+      </x:c>
+      <x:c r="F183" t="str">
+        <x:v>截屏2026-06-08 下午4.49.43.png</x:v>
+      </x:c>
+      <x:c r="G183" t="n">
+        <x:v>1776</x:v>
+      </x:c>
+      <x:c r="H183" t="n">
+        <x:v>1256</x:v>
+      </x:c>
+      <x:c r="I183" t="str">
+        <x:v>images/products/product39/03-detail-02.webp</x:v>
+      </x:c>
+      <x:c r="J183" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184" t="n">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="B184" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C184" t="str">
+        <x:v>product39</x:v>
+      </x:c>
+      <x:c r="D184" t="str">
+        <x:v>商品详情图3</x:v>
+      </x:c>
+      <x:c r="E184" t="str">
+        <x:v>product39/截屏2026-06-08 下午4.48.18.png</x:v>
+      </x:c>
+      <x:c r="F184" t="str">
+        <x:v>截屏2026-06-08 下午4.48.18.png</x:v>
+      </x:c>
+      <x:c r="G184" t="n">
+        <x:v>1782</x:v>
+      </x:c>
+      <x:c r="H184" t="n">
+        <x:v>1258</x:v>
+      </x:c>
+      <x:c r="I184" t="str">
+        <x:v>images/products/product39/04-detail-03.webp</x:v>
+      </x:c>
+      <x:c r="J184" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185" t="n">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="B185" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C185" t="str">
+        <x:v>product39</x:v>
+      </x:c>
+      <x:c r="D185" t="str">
+        <x:v>商品详情图4</x:v>
+      </x:c>
+      <x:c r="E185" t="str">
+        <x:v>product39/截屏2026-06-08 下午4.47.59.png</x:v>
+      </x:c>
+      <x:c r="F185" t="str">
+        <x:v>截屏2026-06-08 下午4.47.59.png</x:v>
+      </x:c>
+      <x:c r="G185" t="n">
+        <x:v>1780</x:v>
+      </x:c>
+      <x:c r="H185" t="n">
+        <x:v>1254</x:v>
+      </x:c>
+      <x:c r="I185" t="str">
+        <x:v>images/products/product39/05-detail-04.webp</x:v>
+      </x:c>
+      <x:c r="J185" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186">
+      <x:c r="A186" t="n">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="B186" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C186" t="str">
+        <x:v>product39</x:v>
+      </x:c>
+      <x:c r="D186" t="str">
+        <x:v>商品详情图5</x:v>
+      </x:c>
+      <x:c r="E186" t="str">
+        <x:v>product39/截屏2026-06-08 下午4.45.48.png</x:v>
+      </x:c>
+      <x:c r="F186" t="str">
+        <x:v>截屏2026-06-08 下午4.45.48.png</x:v>
+      </x:c>
+      <x:c r="G186" t="n">
+        <x:v>1778</x:v>
+      </x:c>
+      <x:c r="H186" t="n">
+        <x:v>1258</x:v>
+      </x:c>
+      <x:c r="I186" t="str">
+        <x:v>images/products/product39/06-detail-05.webp</x:v>
+      </x:c>
+      <x:c r="J186" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187">
+      <x:c r="A187" t="n">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="B187" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C187" t="str">
+        <x:v>product40</x:v>
+      </x:c>
+      <x:c r="D187" t="str">
+        <x:v>商品封面</x:v>
+      </x:c>
+      <x:c r="E187" t="str">
+        <x:v>product40/截屏2026-06-08 下午4.50.50.png</x:v>
+      </x:c>
+      <x:c r="F187" t="str">
+        <x:v>截屏2026-06-08 下午4.50.50.png</x:v>
+      </x:c>
+      <x:c r="G187" t="n">
+        <x:v>1782</x:v>
+      </x:c>
+      <x:c r="H187" t="n">
+        <x:v>1258</x:v>
+      </x:c>
+      <x:c r="I187" t="str">
+        <x:v>images/products/product40/01-cover.webp</x:v>
+      </x:c>
+      <x:c r="J187" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188" t="n">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="B188" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C188" t="str">
+        <x:v>product40</x:v>
+      </x:c>
+      <x:c r="D188" t="str">
+        <x:v>商品详情图1</x:v>
+      </x:c>
+      <x:c r="E188" t="str">
+        <x:v>product40/截屏2026-06-08 下午4.51.14.png</x:v>
+      </x:c>
+      <x:c r="F188" t="str">
+        <x:v>截屏2026-06-08 下午4.51.14.png</x:v>
+      </x:c>
+      <x:c r="G188" t="n">
+        <x:v>1778</x:v>
+      </x:c>
+      <x:c r="H188" t="n">
+        <x:v>1258</x:v>
+      </x:c>
+      <x:c r="I188" t="str">
+        <x:v>images/products/product40/02-detail-01.webp</x:v>
+      </x:c>
+      <x:c r="J188" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A189" t="n">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="B189" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C189" t="str">
+        <x:v>product41</x:v>
+      </x:c>
+      <x:c r="D189" t="str">
+        <x:v>商品封面</x:v>
+      </x:c>
+      <x:c r="E189" t="str">
+        <x:v>product41/截屏2026-06-08 下午5.00.24.png</x:v>
+      </x:c>
+      <x:c r="F189" t="str">
+        <x:v>截屏2026-06-08 下午5.00.24.png</x:v>
+      </x:c>
+      <x:c r="G189" t="n">
+        <x:v>1780</x:v>
+      </x:c>
+      <x:c r="H189" t="n">
+        <x:v>1258</x:v>
+      </x:c>
+      <x:c r="I189" t="str">
+        <x:v>images/products/product41/01-cover.webp</x:v>
+      </x:c>
+      <x:c r="J189" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190">
+      <x:c r="A190" t="n">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="B190" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C190" t="str">
+        <x:v>product41</x:v>
+      </x:c>
+      <x:c r="D190" t="str">
+        <x:v>商品详情图1</x:v>
+      </x:c>
+      <x:c r="E190" t="str">
+        <x:v>product41/截屏2026-06-08 下午4.56.24.png</x:v>
+      </x:c>
+      <x:c r="F190" t="str">
+        <x:v>截屏2026-06-08 下午4.56.24.png</x:v>
+      </x:c>
+      <x:c r="G190" t="n">
+        <x:v>1782</x:v>
+      </x:c>
+      <x:c r="H190" t="n">
+        <x:v>1258</x:v>
+      </x:c>
+      <x:c r="I190" t="str">
+        <x:v>images/products/product41/02-detail-01.webp</x:v>
+      </x:c>
+      <x:c r="J190" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191">
+      <x:c r="A191" t="n">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="B191" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C191" t="str">
+        <x:v>product41</x:v>
+      </x:c>
+      <x:c r="D191" t="str">
+        <x:v>商品详情图2</x:v>
+      </x:c>
+      <x:c r="E191" t="str">
+        <x:v>product41/截屏2026-06-08 下午4.59.48.png</x:v>
+      </x:c>
+      <x:c r="F191" t="str">
+        <x:v>截屏2026-06-08 下午4.59.48.png</x:v>
+      </x:c>
+      <x:c r="G191" t="n">
+        <x:v>1782</x:v>
+      </x:c>
+      <x:c r="H191" t="n">
+        <x:v>1258</x:v>
+      </x:c>
+      <x:c r="I191" t="str">
+        <x:v>images/products/product41/03-detail-02.webp</x:v>
+      </x:c>
+      <x:c r="J191" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192">
+      <x:c r="A192" t="n">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="B192" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C192" t="str">
+        <x:v>product41</x:v>
+      </x:c>
+      <x:c r="D192" t="str">
+        <x:v>商品详情图3</x:v>
+      </x:c>
+      <x:c r="E192" t="str">
+        <x:v>product41/截屏2026-06-08 下午5.00.06.png</x:v>
+      </x:c>
+      <x:c r="F192" t="str">
+        <x:v>截屏2026-06-08 下午5.00.06.png</x:v>
+      </x:c>
+      <x:c r="G192" t="n">
+        <x:v>1780</x:v>
+      </x:c>
+      <x:c r="H192" t="n">
+        <x:v>1256</x:v>
+      </x:c>
+      <x:c r="I192" t="str">
+        <x:v>images/products/product41/04-detail-03.webp</x:v>
+      </x:c>
+      <x:c r="J192" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A193" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="B193" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C193" t="str">
+        <x:v>product41</x:v>
+      </x:c>
+      <x:c r="D193" t="str">
+        <x:v>商品详情图4</x:v>
+      </x:c>
+      <x:c r="E193" t="str">
+        <x:v>product41/截屏2026-06-08 下午4.59.29.png</x:v>
+      </x:c>
+      <x:c r="F193" t="str">
+        <x:v>截屏2026-06-08 下午4.59.29.png</x:v>
+      </x:c>
+      <x:c r="G193" t="n">
+        <x:v>1780</x:v>
+      </x:c>
+      <x:c r="H193" t="n">
+        <x:v>1254</x:v>
+      </x:c>
+      <x:c r="I193" t="str">
+        <x:v>images/products/product41/05-detail-04.webp</x:v>
+      </x:c>
+      <x:c r="J193" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A194" t="n">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="B194" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C194" t="str">
+        <x:v>product42</x:v>
+      </x:c>
+      <x:c r="D194" t="str">
+        <x:v>商品封面</x:v>
+      </x:c>
+      <x:c r="E194" t="str">
+        <x:v>product42/124-宠物友好.jpg</x:v>
+      </x:c>
+      <x:c r="F194" t="str">
+        <x:v>124-宠物友好.jpg</x:v>
+      </x:c>
+      <x:c r="G194" t="n">
+        <x:v>3508</x:v>
+      </x:c>
+      <x:c r="H194" t="n">
+        <x:v>4961</x:v>
+      </x:c>
+      <x:c r="I194" t="str">
+        <x:v>images/products/product42/01-cover.webp</x:v>
+      </x:c>
+      <x:c r="J194" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195" t="n">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="B195" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C195" t="str">
+        <x:v>product42</x:v>
+      </x:c>
+      <x:c r="D195" t="str">
+        <x:v>商品详情图1</x:v>
+      </x:c>
+      <x:c r="E195" t="str">
+        <x:v>product42/124 宠物友好psd.jpg</x:v>
+      </x:c>
+      <x:c r="F195" t="str">
+        <x:v>124 宠物友好psd.jpg</x:v>
+      </x:c>
+      <x:c r="G195" t="n">
+        <x:v>3508</x:v>
+      </x:c>
+      <x:c r="H195" t="n">
+        <x:v>4961</x:v>
+      </x:c>
+      <x:c r="I195" t="str">
+        <x:v>images/products/product42/02-detail-01.webp</x:v>
+      </x:c>
+      <x:c r="J195" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196">
+      <x:c r="A196" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="B196" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C196" t="str">
+        <x:v>product43</x:v>
+      </x:c>
+      <x:c r="D196" t="str">
+        <x:v>商品封面</x:v>
+      </x:c>
+      <x:c r="E196" t="str">
+        <x:v>product43/截屏2026-06-08 下午5.10.47.png</x:v>
+      </x:c>
+      <x:c r="F196" t="str">
+        <x:v>截屏2026-06-08 下午5.10.47.png</x:v>
+      </x:c>
+      <x:c r="G196" t="n">
+        <x:v>1780</x:v>
+      </x:c>
+      <x:c r="H196" t="n">
+        <x:v>1258</x:v>
+      </x:c>
+      <x:c r="I196" t="str">
+        <x:v>images/products/product43/01-cover.webp</x:v>
+      </x:c>
+      <x:c r="J196" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197">
+      <x:c r="A197" t="n">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="B197" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C197" t="str">
+        <x:v>product43</x:v>
+      </x:c>
+      <x:c r="D197" t="str">
+        <x:v>商品详情图1</x:v>
+      </x:c>
+      <x:c r="E197" t="str">
+        <x:v>product43/截屏2026-06-08 下午5.10.26.png</x:v>
+      </x:c>
+      <x:c r="F197" t="str">
+        <x:v>截屏2026-06-08 下午5.10.26.png</x:v>
+      </x:c>
+      <x:c r="G197" t="n">
+        <x:v>1780</x:v>
+      </x:c>
+      <x:c r="H197" t="n">
+        <x:v>1256</x:v>
+      </x:c>
+      <x:c r="I197" t="str">
+        <x:v>images/products/product43/02-detail-01.webp</x:v>
+      </x:c>
+      <x:c r="J197" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198">
+      <x:c r="A198" t="n">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="B198" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C198" t="str">
+        <x:v>product43</x:v>
+      </x:c>
+      <x:c r="D198" t="str">
+        <x:v>商品详情图2</x:v>
+      </x:c>
+      <x:c r="E198" t="str">
+        <x:v>product43/截屏2026-06-08 下午5.09.01.png</x:v>
+      </x:c>
+      <x:c r="F198" t="str">
+        <x:v>截屏2026-06-08 下午5.09.01.png</x:v>
+      </x:c>
+      <x:c r="G198" t="n">
+        <x:v>1780</x:v>
+      </x:c>
+      <x:c r="H198" t="n">
+        <x:v>1256</x:v>
+      </x:c>
+      <x:c r="I198" t="str">
+        <x:v>images/products/product43/03-detail-02.webp</x:v>
+      </x:c>
+      <x:c r="J198" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199">
+      <x:c r="A199" t="n">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="B199" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C199" t="str">
+        <x:v>product43</x:v>
+      </x:c>
+      <x:c r="D199" t="str">
+        <x:v>商品详情图3</x:v>
+      </x:c>
+      <x:c r="E199" t="str">
+        <x:v>product43/截屏2026-06-08 下午5.07.25.png</x:v>
+      </x:c>
+      <x:c r="F199" t="str">
+        <x:v>截屏2026-06-08 下午5.07.25.png</x:v>
+      </x:c>
+      <x:c r="G199" t="n">
+        <x:v>1780</x:v>
+      </x:c>
+      <x:c r="H199" t="n">
+        <x:v>1256</x:v>
+      </x:c>
+      <x:c r="I199" t="str">
+        <x:v>images/products/product43/04-detail-03.webp</x:v>
+      </x:c>
+      <x:c r="J199" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200">
+      <x:c r="A200" t="n">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="B200" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C200" t="str">
+        <x:v>product43</x:v>
+      </x:c>
+      <x:c r="D200" t="str">
+        <x:v>商品详情图4</x:v>
+      </x:c>
+      <x:c r="E200" t="str">
+        <x:v>product43/截屏2026-06-08 下午5.05.57.png</x:v>
+      </x:c>
+      <x:c r="F200" t="str">
+        <x:v>截屏2026-06-08 下午5.05.57.png</x:v>
+      </x:c>
+      <x:c r="G200" t="n">
+        <x:v>1782</x:v>
+      </x:c>
+      <x:c r="H200" t="n">
+        <x:v>1260</x:v>
+      </x:c>
+      <x:c r="I200" t="str">
+        <x:v>images/products/product43/05-detail-04.webp</x:v>
+      </x:c>
+      <x:c r="J200" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201">
+      <x:c r="A201" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="B201" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C201" t="str">
+        <x:v>product44</x:v>
+      </x:c>
+      <x:c r="D201" t="str">
+        <x:v>商品封面</x:v>
+      </x:c>
+      <x:c r="E201" t="str">
+        <x:v>product44/截屏2026-06-08 下午5.19.09.png</x:v>
+      </x:c>
+      <x:c r="F201" t="str">
+        <x:v>截屏2026-06-08 下午5.19.09.png</x:v>
+      </x:c>
+      <x:c r="G201" t="n">
+        <x:v>1074</x:v>
+      </x:c>
+      <x:c r="H201" t="n">
+        <x:v>1520</x:v>
+      </x:c>
+      <x:c r="I201" t="str">
+        <x:v>images/products/product44/01-cover.webp</x:v>
+      </x:c>
+      <x:c r="J201" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202">
+      <x:c r="A202" t="n">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="B202" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C202" t="str">
+        <x:v>product44</x:v>
+      </x:c>
+      <x:c r="D202" t="str">
+        <x:v>商品详情图1</x:v>
+      </x:c>
+      <x:c r="E202" t="str">
+        <x:v>product44/截屏2026-06-08 下午5.20.38.png</x:v>
+      </x:c>
+      <x:c r="F202" t="str">
+        <x:v>截屏2026-06-08 下午5.20.38.png</x:v>
+      </x:c>
+      <x:c r="G202" t="n">
+        <x:v>1082</x:v>
+      </x:c>
+      <x:c r="H202" t="n">
+        <x:v>1528</x:v>
+      </x:c>
+      <x:c r="I202" t="str">
+        <x:v>images/products/product44/02-detail-01.webp</x:v>
+      </x:c>
+      <x:c r="J202" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203">
+      <x:c r="A203" t="n">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="B203" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C203" t="str">
+        <x:v>product45</x:v>
+      </x:c>
+      <x:c r="D203" t="str">
+        <x:v>商品封面</x:v>
+      </x:c>
+      <x:c r="E203" t="str">
+        <x:v>product45/户外模块图_画板 1.png</x:v>
+      </x:c>
+      <x:c r="F203" t="str">
+        <x:v>户外模块图_画板 1.png</x:v>
+      </x:c>
+      <x:c r="G203" t="n">
+        <x:v>4961</x:v>
+      </x:c>
+      <x:c r="H203" t="n">
+        <x:v>3508</x:v>
+      </x:c>
+      <x:c r="I203" t="str">
+        <x:v>images/products/product45/01-cover.webp</x:v>
+      </x:c>
+      <x:c r="J203" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204">
+      <x:c r="A204" t="n">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="B204" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C204" t="str">
+        <x:v>product45</x:v>
+      </x:c>
+      <x:c r="D204" t="str">
+        <x:v>商品详情图1</x:v>
+      </x:c>
+      <x:c r="E204" t="str">
+        <x:v>product45/户外模块图-02.png</x:v>
+      </x:c>
+      <x:c r="F204" t="str">
+        <x:v>户外模块图-02.png</x:v>
+      </x:c>
+      <x:c r="G204" t="n">
+        <x:v>4962</x:v>
+      </x:c>
+      <x:c r="H204" t="n">
+        <x:v>3508</x:v>
+      </x:c>
+      <x:c r="I204" t="str">
+        <x:v>images/products/product45/02-detail-01.webp</x:v>
+      </x:c>
+      <x:c r="J204" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205">
+      <x:c r="A205" t="n">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="B205" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C205" t="str">
+        <x:v>product45</x:v>
+      </x:c>
+      <x:c r="D205" t="str">
+        <x:v>商品详情图2</x:v>
+      </x:c>
+      <x:c r="E205" t="str">
+        <x:v>product45/户外模块图-03.png</x:v>
+      </x:c>
+      <x:c r="F205" t="str">
+        <x:v>户外模块图-03.png</x:v>
+      </x:c>
+      <x:c r="G205" t="n">
+        <x:v>4962</x:v>
+      </x:c>
+      <x:c r="H205" t="n">
+        <x:v>3508</x:v>
+      </x:c>
+      <x:c r="I205" t="str">
+        <x:v>images/products/product45/03-detail-02.webp</x:v>
+      </x:c>
+      <x:c r="J205" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206">
+      <x:c r="A206" t="n">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="B206" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C206" t="str">
+        <x:v>product45</x:v>
+      </x:c>
+      <x:c r="D206" t="str">
+        <x:v>商品详情图3</x:v>
+      </x:c>
+      <x:c r="E206" t="str">
+        <x:v>product45/户外模块图-04.png</x:v>
+      </x:c>
+      <x:c r="F206" t="str">
+        <x:v>户外模块图-04.png</x:v>
+      </x:c>
+      <x:c r="G206" t="n">
+        <x:v>4961</x:v>
+      </x:c>
+      <x:c r="H206" t="n">
+        <x:v>3509</x:v>
+      </x:c>
+      <x:c r="I206" t="str">
+        <x:v>images/products/product45/04-detail-03.webp</x:v>
+      </x:c>
+      <x:c r="J206" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207">
+      <x:c r="A207" t="n">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="B207" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C207" t="str">
+        <x:v>product45</x:v>
+      </x:c>
+      <x:c r="D207" t="str">
+        <x:v>商品详情图4</x:v>
+      </x:c>
+      <x:c r="E207" t="str">
+        <x:v>product45/户外模块图-05.png</x:v>
+      </x:c>
+      <x:c r="F207" t="str">
+        <x:v>户外模块图-05.png</x:v>
+      </x:c>
+      <x:c r="G207" t="n">
+        <x:v>4962</x:v>
+      </x:c>
+      <x:c r="H207" t="n">
+        <x:v>3509</x:v>
+      </x:c>
+      <x:c r="I207" t="str">
+        <x:v>images/products/product45/05-detail-04.webp</x:v>
+      </x:c>
+      <x:c r="J207" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208">
+      <x:c r="A208" t="n">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="B208" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C208" t="str">
+        <x:v>product45</x:v>
+      </x:c>
+      <x:c r="D208" t="str">
+        <x:v>商品详情图5</x:v>
+      </x:c>
+      <x:c r="E208" t="str">
+        <x:v>product45/户外模块图-06.png</x:v>
+      </x:c>
+      <x:c r="F208" t="str">
+        <x:v>户外模块图-06.png</x:v>
+      </x:c>
+      <x:c r="G208" t="n">
+        <x:v>4962</x:v>
+      </x:c>
+      <x:c r="H208" t="n">
+        <x:v>3509</x:v>
+      </x:c>
+      <x:c r="I208" t="str">
+        <x:v>images/products/product45/06-detail-05.webp</x:v>
+      </x:c>
+      <x:c r="J208" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209">
+      <x:c r="A209" t="n">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="B209" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C209" t="str">
+        <x:v>product45</x:v>
+      </x:c>
+      <x:c r="D209" t="str">
+        <x:v>商品详情图6</x:v>
+      </x:c>
+      <x:c r="E209" t="str">
+        <x:v>product45/户外模块图-07.png</x:v>
+      </x:c>
+      <x:c r="F209" t="str">
+        <x:v>户外模块图-07.png</x:v>
+      </x:c>
+      <x:c r="G209" t="n">
+        <x:v>4961</x:v>
+      </x:c>
+      <x:c r="H209" t="n">
+        <x:v>3509</x:v>
+      </x:c>
+      <x:c r="I209" t="str">
+        <x:v>images/products/product45/07-detail-06.webp</x:v>
+      </x:c>
+      <x:c r="J209" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210">
+      <x:c r="A210" t="n">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="B210" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C210" t="str">
+        <x:v>product45</x:v>
+      </x:c>
+      <x:c r="D210" t="str">
+        <x:v>商品详情图7</x:v>
+      </x:c>
+      <x:c r="E210" t="str">
+        <x:v>product45/户外模块图-08.png</x:v>
+      </x:c>
+      <x:c r="F210" t="str">
+        <x:v>户外模块图-08.png</x:v>
+      </x:c>
+      <x:c r="G210" t="n">
+        <x:v>4962</x:v>
+      </x:c>
+      <x:c r="H210" t="n">
+        <x:v>3509</x:v>
+      </x:c>
+      <x:c r="I210" t="str">
+        <x:v>images/products/product45/08-detail-07.webp</x:v>
+      </x:c>
+      <x:c r="J210" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211">
+      <x:c r="A211" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="B211" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C211" t="str">
+        <x:v>product45</x:v>
+      </x:c>
+      <x:c r="D211" t="str">
+        <x:v>商品详情图8</x:v>
+      </x:c>
+      <x:c r="E211" t="str">
+        <x:v>product45/户外模块图-09.png</x:v>
+      </x:c>
+      <x:c r="F211" t="str">
+        <x:v>户外模块图-09.png</x:v>
+      </x:c>
+      <x:c r="G211" t="n">
+        <x:v>4962</x:v>
+      </x:c>
+      <x:c r="H211" t="n">
+        <x:v>3509</x:v>
+      </x:c>
+      <x:c r="I211" t="str">
+        <x:v>images/products/product45/09-detail-08.webp</x:v>
+      </x:c>
+      <x:c r="J211" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212">
+      <x:c r="A212" t="n">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="B212" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C212" t="str">
+        <x:v>product45</x:v>
+      </x:c>
+      <x:c r="D212" t="str">
+        <x:v>商品详情图9</x:v>
+      </x:c>
+      <x:c r="E212" t="str">
+        <x:v>product45/户外模块图-10.png</x:v>
+      </x:c>
+      <x:c r="F212" t="str">
+        <x:v>户外模块图-10.png</x:v>
+      </x:c>
+      <x:c r="G212" t="n">
+        <x:v>4961</x:v>
+      </x:c>
+      <x:c r="H212" t="n">
+        <x:v>3509</x:v>
+      </x:c>
+      <x:c r="I212" t="str">
+        <x:v>images/products/product45/10-detail-09.webp</x:v>
+      </x:c>
+      <x:c r="J212" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213">
+      <x:c r="A213" t="n">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="B213" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C213" t="str">
+        <x:v>product45</x:v>
+      </x:c>
+      <x:c r="D213" t="str">
+        <x:v>商品详情图10</x:v>
+      </x:c>
+      <x:c r="E213" t="str">
+        <x:v>product45/户外模块图-11.png</x:v>
+      </x:c>
+      <x:c r="F213" t="str">
+        <x:v>户外模块图-11.png</x:v>
+      </x:c>
+      <x:c r="G213" t="n">
+        <x:v>4962</x:v>
+      </x:c>
+      <x:c r="H213" t="n">
+        <x:v>3509</x:v>
+      </x:c>
+      <x:c r="I213" t="str">
+        <x:v>images/products/product45/11-detail-10.webp</x:v>
+      </x:c>
+      <x:c r="J213" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214">
+      <x:c r="A214" t="n">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="B214" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C214" t="str">
+        <x:v>product45</x:v>
+      </x:c>
+      <x:c r="D214" t="str">
+        <x:v>商品详情图11</x:v>
+      </x:c>
+      <x:c r="E214" t="str">
+        <x:v>product45/户外模块图-12.png</x:v>
+      </x:c>
+      <x:c r="F214" t="str">
+        <x:v>户外模块图-12.png</x:v>
+      </x:c>
+      <x:c r="G214" t="n">
+        <x:v>4962</x:v>
+      </x:c>
+      <x:c r="H214" t="n">
+        <x:v>3509</x:v>
+      </x:c>
+      <x:c r="I214" t="str">
+        <x:v>images/products/product45/12-detail-11.webp</x:v>
+      </x:c>
+      <x:c r="J214" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215">
+      <x:c r="A215" t="n">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="B215" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C215" t="str">
+        <x:v>product45</x:v>
+      </x:c>
+      <x:c r="D215" t="str">
+        <x:v>商品详情图12</x:v>
+      </x:c>
+      <x:c r="E215" t="str">
+        <x:v>product45/户外模块图-13.png</x:v>
+      </x:c>
+      <x:c r="F215" t="str">
+        <x:v>户外模块图-13.png</x:v>
+      </x:c>
+      <x:c r="G215" t="n">
+        <x:v>4961</x:v>
+      </x:c>
+      <x:c r="H215" t="n">
+        <x:v>3508</x:v>
+      </x:c>
+      <x:c r="I215" t="str">
+        <x:v>images/products/product45/13-detail-12.webp</x:v>
+      </x:c>
+      <x:c r="J215" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216">
+      <x:c r="A216" t="n">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="B216" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C216" t="str">
+        <x:v>product45</x:v>
+      </x:c>
+      <x:c r="D216" t="str">
+        <x:v>商品详情图13</x:v>
+      </x:c>
+      <x:c r="E216" t="str">
+        <x:v>product45/户外模块图-14.png</x:v>
+      </x:c>
+      <x:c r="F216" t="str">
+        <x:v>户外模块图-14.png</x:v>
+      </x:c>
+      <x:c r="G216" t="n">
+        <x:v>4962</x:v>
+      </x:c>
+      <x:c r="H216" t="n">
+        <x:v>3508</x:v>
+      </x:c>
+      <x:c r="I216" t="str">
+        <x:v>images/products/product45/14-detail-13.webp</x:v>
+      </x:c>
+      <x:c r="J216" t="str">
+        <x:v>已转 WebP 并接入网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217">
+      <x:c r="A217" t="n">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="B217" t="str">
+        <x:v>商品图片</x:v>
+      </x:c>
+      <x:c r="C217" t="str">
+        <x:v>product45</x:v>
+      </x:c>
+      <x:c r="D217" t="str">
+        <x:v>商品详情图14</x:v>
+      </x:c>
+      <x:c r="E217" t="str">
+        <x:v>product45/户外模块图-15.png</x:v>
+      </x:c>
+      <x:c r="F217" t="str">
+        <x:v>户外模块图-15.png</x:v>
+      </x:c>
+      <x:c r="G217" t="n">
+        <x:v>4961</x:v>
+      </x:c>
+      <x:c r="H217" t="n">
+        <x:v>3509</x:v>
+      </x:c>
+      <x:c r="I217" t="str">
+        <x:v>images/products/product45/15-detail-14.webp</x:v>
+      </x:c>
+      <x:c r="J217" t="str">
         <x:v>已转 WebP 并接入网站</x:v>
       </x:c>
     </x:row>
@@ -10846,4 +13669,537 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="3.9000000953674316" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="8.210000038146973" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="7.809999942779541" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="34.86000061035156" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="3.9000000953674316" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="34.86000061035156" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="68.91000366210938" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="101.08000183105469" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="50" t="str">
+        <x:v>编号</x:v>
+      </x:c>
+      <x:c r="B1" s="50" t="str">
+        <x:v>商品名</x:v>
+      </x:c>
+      <x:c r="C1" s="50" t="str">
+        <x:v>英文名</x:v>
+      </x:c>
+      <x:c r="D1" s="50" t="str">
+        <x:v>分类</x:v>
+      </x:c>
+      <x:c r="E1" s="50" t="str">
+        <x:v>图片数量</x:v>
+      </x:c>
+      <x:c r="F1" s="50" t="str">
+        <x:v>封面路径</x:v>
+      </x:c>
+      <x:c r="G1" s="50" t="str">
+        <x:v>价格</x:v>
+      </x:c>
+      <x:c r="H1" s="50" t="str">
+        <x:v>标签</x:v>
+      </x:c>
+      <x:c r="I1" s="50" t="str">
+        <x:v>补齐说明</x:v>
+      </x:c>
+      <x:c r="J1" s="50" t="str">
+        <x:v>备注</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>P031</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>景观人物/植物素材</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>product31</x:v>
+      </x:c>
+      <x:c r="D2" t="str">
+        <x:v>Plant Assets</x:v>
+      </x:c>
+      <x:c r="E2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F2" t="str">
+        <x:v>images/products/product31/01-cover.webp</x:v>
+      </x:c>
+      <x:c r="G2" t="n">
+        <x:v>9.9</x:v>
+      </x:c>
+      <x:c r="H2" t="str">
+        <x:v>People, Plant, Landscape, PNG/AI</x:v>
+      </x:c>
+      <x:c r="I2" t="str">
+        <x:v>景观人物与植物素材合集，适合平面、分析图和场景氛围表达。</x:v>
+      </x:c>
+      <x:c r="J2" t="str">
+        <x:v>新增 product31；图片已转 WebP 并接入网站。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>P032</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>黑白人物素材</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>product32</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>People Assets</x:v>
+      </x:c>
+      <x:c r="E3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F3" t="str">
+        <x:v>images/products/product32/01-cover.webp</x:v>
+      </x:c>
+      <x:c r="G3" t="n">
+        <x:v>8.8</x:v>
+      </x:c>
+      <x:c r="H3" t="str">
+        <x:v>People, Black White, Figure, PNG/AI</x:v>
+      </x:c>
+      <x:c r="I3" t="str">
+        <x:v>黑白人物剪影与线稿素材，适合分析图、平面图和作品集排版。</x:v>
+      </x:c>
+      <x:c r="J3" t="str">
+        <x:v>新增 product32；图片已转 WebP 并接入网站。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>P033</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>高级感分析图模版素材</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>product33</x:v>
+      </x:c>
+      <x:c r="D4" t="str">
+        <x:v>Module Diagrams</x:v>
+      </x:c>
+      <x:c r="E4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F4" t="str">
+        <x:v>images/products/product33/01-cover.webp</x:v>
+      </x:c>
+      <x:c r="G4" t="n">
+        <x:v>12.8</x:v>
+      </x:c>
+      <x:c r="H4" t="str">
+        <x:v>Module, Diagram, Analysis, AI/Psd</x:v>
+      </x:c>
+      <x:c r="I4" t="str">
+        <x:v>高级感分析图模版素材，适合作品集前期分析、策略图和概念表达。</x:v>
+      </x:c>
+      <x:c r="J4" t="str">
+        <x:v>新增 product33；图片已转 WebP 并接入网站。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>P034</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>插画风动植物/人物素材</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>product34</x:v>
+      </x:c>
+      <x:c r="D5" t="str">
+        <x:v>Animal Assets</x:v>
+      </x:c>
+      <x:c r="E5" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F5" t="str">
+        <x:v>images/products/product34/01-cover.webp</x:v>
+      </x:c>
+      <x:c r="G5" t="n">
+        <x:v>9.9</x:v>
+      </x:c>
+      <x:c r="H5" t="str">
+        <x:v>People, Plant, Animal, Illustration</x:v>
+      </x:c>
+      <x:c r="I5" t="str">
+        <x:v>插画风动植物与人物素材，适合自然场景、活动氛围和作品集点缀。</x:v>
+      </x:c>
+      <x:c r="J5" t="str">
+        <x:v>新增 product34；图片已转 WebP 并接入网站。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>P035</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>蓝色系人物/植物素材</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>product35</x:v>
+      </x:c>
+      <x:c r="D6" t="str">
+        <x:v>People Assets</x:v>
+      </x:c>
+      <x:c r="E6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F6" t="str">
+        <x:v>images/products/product35/01-cover.webp</x:v>
+      </x:c>
+      <x:c r="G6" t="n">
+        <x:v>8.8</x:v>
+      </x:c>
+      <x:c r="H6" t="str">
+        <x:v>People, Plant, Blue, Illustration</x:v>
+      </x:c>
+      <x:c r="I6" t="str">
+        <x:v>蓝色系人物与植物素材，可用于平面、剖面和分析图的清爽表达。</x:v>
+      </x:c>
+      <x:c r="J6" t="str">
+        <x:v>新增 product35；图片已转 WebP 并接入网站。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>P036</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>高级感前期分析模版</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>product36</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>Module Diagrams</x:v>
+      </x:c>
+      <x:c r="E7" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
+        <x:v>images/products/product36/01-cover.webp</x:v>
+      </x:c>
+      <x:c r="G7" t="n">
+        <x:v>12.8</x:v>
+      </x:c>
+      <x:c r="H7" t="str">
+        <x:v>Module, Diagram, Analysis, AI/Psd</x:v>
+      </x:c>
+      <x:c r="I7" t="str">
+        <x:v>高级感前期分析模版，适合场地分析、空间关系和设计策略表达。</x:v>
+      </x:c>
+      <x:c r="J7" t="str">
+        <x:v>新增 product36；图片已转 WebP 并接入网站。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>P037</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>拼贴感前期分析模版</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>product37</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>Module Diagrams</x:v>
+      </x:c>
+      <x:c r="E8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F8" t="str">
+        <x:v>images/products/product37/01-cover.webp</x:v>
+      </x:c>
+      <x:c r="G8" t="n">
+        <x:v>12.8</x:v>
+      </x:c>
+      <x:c r="H8" t="str">
+        <x:v>Module, Collage, Diagram, AI/Psd</x:v>
+      </x:c>
+      <x:c r="I8" t="str">
+        <x:v>拼贴感前期分析模版，适合图文混排、概念推演和作品集表达。</x:v>
+      </x:c>
+      <x:c r="J8" t="str">
+        <x:v>新增 product37；图片已转 WebP 并接入网站。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>P038</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>时间线分析模版</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>product38</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>Module Diagrams</x:v>
+      </x:c>
+      <x:c r="E9" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F9" t="str">
+        <x:v>images/products/product38/01-cover.webp</x:v>
+      </x:c>
+      <x:c r="G9" t="n">
+        <x:v>12.8</x:v>
+      </x:c>
+      <x:c r="H9" t="str">
+        <x:v>Module, Timeline, Diagram, AI/Psd</x:v>
+      </x:c>
+      <x:c r="I9" t="str">
+        <x:v>时间线分析模版，适合阶段梳理、流程表达和作品集逻辑展示。</x:v>
+      </x:c>
+      <x:c r="J9" t="str">
+        <x:v>新增 product38；图片已转 WebP 并接入网站。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>P039</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>自然教育模块素材</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>product39</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
+        <x:v>Module Diagrams</x:v>
+      </x:c>
+      <x:c r="E10" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F10" t="str">
+        <x:v>images/products/product39/01-cover.webp</x:v>
+      </x:c>
+      <x:c r="G10" t="n">
+        <x:v>15.8</x:v>
+      </x:c>
+      <x:c r="H10" t="str">
+        <x:v>Module, Nature Education, Diagram, AI/Psd</x:v>
+      </x:c>
+      <x:c r="I10" t="str">
+        <x:v>自然教育主题模块素材，适合户外教育、自然观察和场地活动分析。</x:v>
+      </x:c>
+      <x:c r="J10" t="str">
+        <x:v>新增 product39；图片已转 WebP 并接入网站。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>P040</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>高级感剖面素材</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>product40</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>Animal Assets</x:v>
+      </x:c>
+      <x:c r="E11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F11" t="str">
+        <x:v>images/products/product40/01-cover.webp</x:v>
+      </x:c>
+      <x:c r="G11" t="n">
+        <x:v>9.9</x:v>
+      </x:c>
+      <x:c r="H11" t="str">
+        <x:v>People, Plant, Animal, Section</x:v>
+      </x:c>
+      <x:c r="I11" t="str">
+        <x:v>高级感剖面素材，包含人物、植物与动物场景元素，适合剖面表达和图面点缀。</x:v>
+      </x:c>
+      <x:c r="J11" t="str">
+        <x:v>新增 product40；图片已转 WebP 并接入网站。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>P041</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>高级感作品集分析图模版</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>product41</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>Module Diagrams</x:v>
+      </x:c>
+      <x:c r="E12" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F12" t="str">
+        <x:v>images/products/product41/01-cover.webp</x:v>
+      </x:c>
+      <x:c r="G12" t="n">
+        <x:v>12.8</x:v>
+      </x:c>
+      <x:c r="H12" t="str">
+        <x:v>Module, Portfolio, Diagram, AI/Psd</x:v>
+      </x:c>
+      <x:c r="I12" t="str">
+        <x:v>高级感作品集分析图模版，适合版式整理、场地分析和设计叙事。</x:v>
+      </x:c>
+      <x:c r="J12" t="str">
+        <x:v>新增 product41；图片已转 WebP 并接入网站。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>P042</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>宠物友好设计素材</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>product42</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>Animal Assets</x:v>
+      </x:c>
+      <x:c r="E13" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F13" t="str">
+        <x:v>images/products/product42/01-cover.webp</x:v>
+      </x:c>
+      <x:c r="G13" t="n">
+        <x:v>8.8</x:v>
+      </x:c>
+      <x:c r="H13" t="str">
+        <x:v>Pet, Animal, Plant, PSD</x:v>
+      </x:c>
+      <x:c r="I13" t="str">
+        <x:v>宠物友好主题设计素材，适合宠物活动空间、社区场景和景观分析表达。</x:v>
+      </x:c>
+      <x:c r="J13" t="str">
+        <x:v>新增 product42；图片已转 WebP 并接入网站。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>P043</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>人物分析模版素材</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>product43</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>Module Diagrams</x:v>
+      </x:c>
+      <x:c r="E14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F14" t="str">
+        <x:v>images/products/product43/01-cover.webp</x:v>
+      </x:c>
+      <x:c r="G14" t="n">
+        <x:v>12.8</x:v>
+      </x:c>
+      <x:c r="H14" t="str">
+        <x:v>Module, People Analysis, Diagram, AI/Psd</x:v>
+      </x:c>
+      <x:c r="I14" t="str">
+        <x:v>人物分析模版素材，适合人群行为、活动路径和空间使用分析。</x:v>
+      </x:c>
+      <x:c r="J14" t="str">
+        <x:v>新增 product43；图片已转 WebP 并接入网站。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>P044</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>景观建筑户外素材</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>product44</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>Animal Assets</x:v>
+      </x:c>
+      <x:c r="E15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F15" t="str">
+        <x:v>images/products/product44/01-cover.webp</x:v>
+      </x:c>
+      <x:c r="G15" t="n">
+        <x:v>9.9</x:v>
+      </x:c>
+      <x:c r="H15" t="str">
+        <x:v>People, Plant, Animal, Outdoor</x:v>
+      </x:c>
+      <x:c r="I15" t="str">
+        <x:v>景观建筑户外素材，包含人物、植物与动物场景元素，适合户外空间氛围表达。</x:v>
+      </x:c>
+      <x:c r="J15" t="str">
+        <x:v>新增 product44；图片已转 WebP 并接入网站。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>P045</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>景观建筑户外设计模块</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>product45</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>Module Diagrams</x:v>
+      </x:c>
+      <x:c r="E16" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>images/products/product45/01-cover.webp</x:v>
+      </x:c>
+      <x:c r="G16" t="n">
+        <x:v>14.8</x:v>
+      </x:c>
+      <x:c r="H16" t="str">
+        <x:v>Module, Outdoor, Landscape, AI/Psd</x:v>
+      </x:c>
+      <x:c r="I16" t="str">
+        <x:v>景观建筑户外设计模块，适合节点设计、活动场景和作品集模块表达。</x:v>
+      </x:c>
+      <x:c r="J16" t="str">
+        <x:v>新增 product45；图片已转 WebP 并接入网站。 另有 07-detail-06.webp ～ 15-detail-14.webp，已接入网站 images 列表。</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>